--- a/sample/CS_登記簿自動入力.xlsx
+++ b/sample/CS_登記簿自動入力.xlsx
@@ -8,13 +8,53 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoshidasan/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68BFC2BF-82AE-CB4F-BD51-DE8E48ABF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{C20F8D5E-52A4-9C43-B702-4C781A866527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20100" xr2:uid="{D8239FF8-0CBD-1E45-B595-17EEB0B6B7DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="運用" sheetId="2" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <definedNames>
+    <definedName name="a">DATE(YEAR(Loan_Start),MONTH(Loan_Start)+Payment_Number,DAY(Loan_Start))</definedName>
+    <definedName name="Beg_Bal">[2]ローン計画書!$C$18:$C$497</definedName>
+    <definedName name="daa">#N/A</definedName>
+    <definedName name="End_Bal">[2]ローン計画書!$I$18:$I$497</definedName>
+    <definedName name="Extra_Pay">[2]ローン計画書!$E$18:$E$497</definedName>
+    <definedName name="Full_Print">[2]ローン計画書!$A$1:$J$497</definedName>
+    <definedName name="Header_Row">ROW([2]ローン計画書!$17:$17)</definedName>
+    <definedName name="Int">[2]ローン計画書!$H$18:$H$497</definedName>
+    <definedName name="Interest_Rate">[2]ローン計画書!$D$6</definedName>
+    <definedName name="Last_Row">IF(Values_Entered,Header_Row+Number_of_Payments,Header_Row)</definedName>
+    <definedName name="Loan_Amount">[2]ローン計画書!$D$5</definedName>
+    <definedName name="Loan_Start">[2]ローン計画書!$D$9</definedName>
+    <definedName name="Loan_Years">[2]ローン計画書!$D$7</definedName>
+    <definedName name="Num_Pmt_Per_Year">[2]ローン計画書!$D$8</definedName>
+    <definedName name="Number_of_Payments">MATCH(0.01,End_Bal,-1)+1</definedName>
+    <definedName name="Pay_Num">[2]ローン計画書!$A$18:$A$497</definedName>
+    <definedName name="Payment_Date">DATE(YEAR(Loan_Start),MONTH(Loan_Start)+Payment_Number,DAY(Loan_Start))</definedName>
+    <definedName name="Princ">[2]ローン計画書!$G$18:$G$497</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">運用!$A$1:$AA$39</definedName>
+    <definedName name="Print_Area_Reset">OFFSET(Full_Print,0,0,Last_Row)</definedName>
+    <definedName name="Sched_Pay">[2]ローン計画書!$D$18:$D$497</definedName>
+    <definedName name="Scheduled_Extra_Payments">[2]ローン計画書!$D$10</definedName>
+    <definedName name="Scheduled_Monthly_Payment">[2]ローン計画書!$J$5</definedName>
+    <definedName name="Total_Pay">[2]ローン計画書!$F$18:$F$497</definedName>
+    <definedName name="Total_Payment">Scheduled_Payment+Extra_Payment</definedName>
+    <definedName name="Values_Entered">IF(Loan_Amount*Interest_Rate*Loan_Years*Loan_Start&gt;0,1,0)</definedName>
+    <definedName name="あ">IF(Loan_Amount*Interest_Rate*Loan_Years*Loan_Start&gt;0,1,0)</definedName>
+    <definedName name="ああ">MATCH(0.01,End_Bal,-1)+1</definedName>
+    <definedName name="あああ">DATE(YEAR([0]!Loan_Start),MONTH([0]!Loan_Start)+Payment_Number,DAY([0]!Loan_Start))</definedName>
+    <definedName name="繰上返済">Scheduled_Payment+Extra_Payment</definedName>
+    <definedName name="清算説明">#N/A</definedName>
+    <definedName name="買主様の収支">DATE(YEAR([0]!Loan_Start),MONTH([0]!Loan_Start)+Payment_Number,DAY([0]!Loan_Start))</definedName>
+    <definedName name="敷金等">[3]項目!$E$68:$E$71</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -40,13 +80,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="69">
   <si>
     <t>物件概要</t>
     <rPh sb="0" eb="4">
       <t>ブッケンガイヨウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>管理会社</t>
@@ -56,11 +96,11 @@
     <rPh sb="2" eb="4">
       <t>ガイシャ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>賃貸管理会社</t>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>建物管理会社</t>
@@ -73,21 +113,21 @@
     <rPh sb="4" eb="6">
       <t>ガイシャ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ローン概要</t>
     <rPh sb="3" eb="5">
       <t>ガイヨウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ローン会社</t>
     <rPh sb="3" eb="5">
       <t>カイシャ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>融資額</t>
@@ -97,14 +137,14 @@
     <rPh sb="2" eb="3">
       <t>ガク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ご残債</t>
     <rPh sb="1" eb="3">
       <t>ザンサイ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>頭金(万)</t>
@@ -114,7 +154,7 @@
     <rPh sb="3" eb="4">
       <t>マン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>借換時期</t>
@@ -124,14 +164,14 @@
     <rPh sb="2" eb="4">
       <t>ジキ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>金利</t>
     <rPh sb="0" eb="2">
       <t>キンリ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>返済期間</t>
@@ -141,7 +181,7 @@
     <rPh sb="2" eb="4">
       <t>キカン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>～</t>
@@ -151,14 +191,14 @@
     <rPh sb="0" eb="2">
       <t>シュウニュウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>家賃</t>
     <rPh sb="0" eb="2">
       <t>ヤチン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>ローン返済額</t>
@@ -168,28 +208,28 @@
     <rPh sb="5" eb="6">
       <t>ガク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>支出</t>
     <rPh sb="0" eb="2">
       <t>シシュツ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>管理費</t>
     <rPh sb="0" eb="3">
       <t>カンリヒ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>修繕費</t>
     <rPh sb="0" eb="3">
       <t>シュウゼンヒ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <r>
@@ -211,42 +251,42 @@
     <rPh sb="4" eb="6">
       <t>ホケン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>手数料</t>
     <rPh sb="0" eb="3">
       <t>テスウリョウ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>固定資産税</t>
     <rPh sb="0" eb="5">
       <t>コテイシサンゼイ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>収支</t>
     <rPh sb="0" eb="2">
       <t>シュウシ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>月間</t>
     <rPh sb="0" eb="2">
       <t>ゲッカン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>年間</t>
     <rPh sb="0" eb="2">
       <t>ネンカン</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>完済までの
@@ -263,14 +303,14 @@
     <rPh sb="10" eb="11">
       <t>ガク</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>駅徒歩</t>
     <rPh sb="0" eb="3">
       <t>エキトホ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
   </si>
   <si>
     <t>物件住所</t>
@@ -280,14 +320,325 @@
     <rPh sb="2" eb="4">
       <t>ジュウショ</t>
     </rPh>
-    <phoneticPr fontId="9"/>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>資産運用コンサルティングシート</t>
+    <rPh sb="0" eb="2">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ウンヨウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>様</t>
+    <rPh sb="0" eb="1">
+      <t>サマ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>株式会社エルズホーム</t>
+  </si>
+  <si>
+    <t>1.　現在の運用状況</t>
+    <rPh sb="3" eb="5">
+      <t>ゲンザイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ウンヨウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジョウキョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>〒153-0043　東京都目黒区東山1-4-4</t>
+  </si>
+  <si>
+    <t>TEL：03-5794-5151　FAX：03-5794-5161</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>■年表</t>
+    <rPh sb="1" eb="3">
+      <t>ネンピョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>購入時の築年数</t>
+    <rPh sb="0" eb="3">
+      <t>コウニュウジ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>チクネンスウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>35年ローンの場合：</t>
+    <rPh sb="2" eb="3">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>Maxローン年数 ：</t>
+    <rPh sb="6" eb="8">
+      <t>ネンスウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>※不明な場合は購入時期に直接入力</t>
+    <rPh sb="1" eb="3">
+      <t>フメイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="7" eb="11">
+      <t>コウニュウジキ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>チョクセツニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>2022年</t>
+    <rPh sb="4" eb="5">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ご年齢表</t>
+    <rPh sb="1" eb="3">
+      <t>ネンレイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>年表</t>
+    <rPh sb="0" eb="2">
+      <t>ネンピョウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>購入時期</t>
+    <rPh sb="0" eb="2">
+      <t>コウニュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジキ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>→</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>現在</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>退職</t>
+    <rPh sb="0" eb="2">
+      <t>タイショク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>完済</t>
+    <rPh sb="0" eb="2">
+      <t>カンサイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>オーナー様</t>
+    <rPh sb="4" eb="5">
+      <t>サマ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>い</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>う</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>え</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ライフイベント</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TOTAL 収支</t>
+    <rPh sb="6" eb="8">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>合計の収支</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>シュウシ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>※すべて想定の数値です。</t>
+    <rPh sb="4" eb="6">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>スウチ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ATBB</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>日付</t>
+    <rPh sb="0" eb="2">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>管積</t>
+    <rPh sb="0" eb="2">
+      <t>カンツミ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>㎡計算</t>
+    <rPh sb="1" eb="3">
+      <t>ケイサン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>残債</t>
+    <rPh sb="0" eb="2">
+      <t>ザンサイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>元金</t>
+    <rPh sb="0" eb="2">
+      <t>ガンキン</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1カ月元金減り</t>
+    <rPh sb="2" eb="3">
+      <t>ゲツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガンキン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1年元金減り</t>
+    <rPh sb="1" eb="2">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガンキン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ヘ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>購入</t>
+    <rPh sb="0" eb="2">
+      <t>コウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>譲渡税時期</t>
+    <rPh sb="0" eb="3">
+      <t>ジョウトゼイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジキ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>購入時築</t>
+    <rPh sb="0" eb="3">
+      <t>コウニュウジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>完済時築</t>
+    <rPh sb="0" eb="3">
+      <t>カンサイジ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>集金代行</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="16">
+  <numFmts count="24">
     <numFmt numFmtId="176" formatCode="###0&quot;階建&quot;"/>
     <numFmt numFmtId="177" formatCode="#,##0&quot;戸&quot;"/>
     <numFmt numFmtId="178" formatCode="###0&quot;号室&quot;"/>
@@ -304,16 +655,16 @@
     <numFmt numFmtId="189" formatCode="General&quot;年&quot;"/>
     <numFmt numFmtId="190" formatCode="#,##0&quot;円／年&quot;"/>
     <numFmt numFmtId="191" formatCode="#,##0&quot;円／月&quot;"/>
+    <numFmt numFmtId="192" formatCode="General&quot;様&quot;"/>
+    <numFmt numFmtId="193" formatCode="m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="194" formatCode="&quot;築&quot;###0&quot;年の時に購入&quot;"/>
+    <numFmt numFmtId="195" formatCode="0&quot;年&quot;"/>
+    <numFmt numFmtId="196" formatCode="0&quot;年&quot;&quot;後&quot;"/>
+    <numFmt numFmtId="197" formatCode="0&quot;歳&quot;"/>
+    <numFmt numFmtId="198" formatCode="&quot;&quot;0&quot;年&quot;"/>
+    <numFmt numFmtId="199" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="48">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -448,8 +799,197 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color indexed="8"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="44"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="44"/>
+      <color theme="0"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0" tint="-0.249977111117893"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FF0000FF"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color rgb="FFFF0000"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="BIZ UDPゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -486,8 +1026,62 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76933C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="54">
+  <borders count="110">
     <border>
       <left/>
       <right/>
@@ -1111,452 +1705,1827 @@
     </border>
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
       <bottom style="double">
-        <color indexed="64"/>
+        <color rgb="FFFF0000"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="192" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="28" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="53" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="189" fontId="30" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="193" fontId="30" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="54" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="194" fontId="33" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="35" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="195" fontId="38" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="56" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="59" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="60" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="196" fontId="38" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="196" fontId="38" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="58" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="59" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="60" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="13" fillId="2" borderId="62" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="13" fillId="2" borderId="63" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="39" fillId="2" borderId="64" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="39" fillId="2" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="13" fillId="2" borderId="64" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="197" fontId="13" fillId="2" borderId="65" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="40" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="13" fillId="2" borderId="69" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="13" fillId="2" borderId="70" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="13" fillId="2" borderId="71" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="13" fillId="2" borderId="72" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="195" fontId="10" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="198" fontId="41" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="198" fontId="42" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="73" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="0" borderId="75" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="2" borderId="75" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="76" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="77" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="0" borderId="78" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="38" fillId="2" borderId="78" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="12" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="12" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="184" fontId="12" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="61" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="37" fillId="0" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="1" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="197" fontId="37" fillId="2" borderId="61" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="0" borderId="23" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="185" fontId="11" fillId="0" borderId="25" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="37" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="43" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="43" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="186" fontId="11" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="186" fontId="11" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="186" fontId="11" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="43" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="43" fillId="0" borderId="61" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="43" fillId="2" borderId="61" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="186" fontId="13" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="186" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="188" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="37" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="38" fontId="37" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="5" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="189" fontId="5" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="79" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="80" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="37" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="182" fontId="16" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="16" fillId="0" borderId="38" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="16" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="44" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" textRotation="255"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="42" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="45" fillId="0" borderId="81" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="82" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="83" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="79" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="80" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="84" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="2" borderId="23" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="2" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="17" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="81" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="82" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="83" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="190" fontId="17" fillId="0" borderId="43" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="190" fontId="17" fillId="0" borderId="44" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="191" fontId="17" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="79" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="80" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="84" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="66" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="67" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="47" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="49" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="50" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="51" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="50" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="38" fontId="18" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="190" fontId="18" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="190" fontId="18" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="20" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="19" fillId="0" borderId="85" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="86" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="87" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="0" borderId="53" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="199" fontId="23" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="88" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="89" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="33" fillId="0" borderId="90" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="181" fontId="33" fillId="12" borderId="90" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="91" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="0" borderId="92" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="9" fillId="0" borderId="72" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="33" fillId="0" borderId="93" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="94" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="95" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="33" fillId="0" borderId="96" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="60" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="90" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="187" fontId="33" fillId="0" borderId="97" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="98" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="10" fillId="0" borderId="99" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="11" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="100" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="101" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="102" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="71" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="55" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="182" fontId="16" fillId="0" borderId="72" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" xfId="1" applyFont="1" applyFill="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="103" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="46" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="104" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="105" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="106" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="107" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="108" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="38" fontId="47" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="47" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="47" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="48" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="109" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="17" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="17" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="41" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="18" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="10" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="10" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="183" fontId="10" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="184" fontId="13" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="185" fontId="12" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="185" fontId="12" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="185" fontId="12" fillId="0" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="186" fontId="12" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="186" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="186" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="186" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="186" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="50" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="183" fontId="9" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="183" fontId="9" fillId="0" borderId="29" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
+  <cellStyles count="4">
+    <cellStyle name="桁区切り 2" xfId="2" xr:uid="{17D3D0B9-24A9-DC43-A077-812E66736343}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="1" xr:uid="{D10B5235-8F92-4249-A33F-5E092F551C4D}"/>
+    <cellStyle name="標準 2 2" xfId="3" xr:uid="{2707C768-CBE8-904E-A224-43E05972C4BB}"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="33">
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF0000FF"/>
       </font>
     </dxf>
     <dxf>
@@ -1569,7 +3538,55 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1594,20 +3611,84 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color theme="0"/>
       </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1632,6 +3713,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0000FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFF0000"/>
       </font>
     </dxf>
@@ -1647,6 +3748,13 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1658,6 +3766,232 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="銀行"/>
+      <sheetName val="表紙"/>
+      <sheetName val="運用"/>
+      <sheetName val="過去売却"/>
+      <sheetName val="下落"/>
+      <sheetName val="管積"/>
+      <sheetName val="空室・完済売却"/>
+      <sheetName val="回収率"/>
+      <sheetName val="購入時"/>
+      <sheetName val="売却S"/>
+      <sheetName val="5年後"/>
+      <sheetName val="10年後"/>
+      <sheetName val="売却S 差額借入S"/>
+      <sheetName val="○年後"/>
+      <sheetName val="譲渡税"/>
+      <sheetName val="還付計算"/>
+      <sheetName val="生命保険"/>
+      <sheetName val="利回り表"/>
+      <sheetName val="残債evi無"/>
+      <sheetName val="残債evi有"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4">
+        <row r="12">
+          <cell r="C12" t="str">
+            <v/>
+          </cell>
+          <cell r="F12" t="str">
+            <v/>
+          </cell>
+          <cell r="I12" t="str">
+            <v/>
+          </cell>
+          <cell r="L12" t="str">
+            <v/>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6">
+        <row r="71">
+          <cell r="C71" t="str">
+            <v/>
+          </cell>
+          <cell r="F71" t="str">
+            <v/>
+          </cell>
+          <cell r="I71" t="str">
+            <v/>
+          </cell>
+          <cell r="L71" t="str">
+            <v/>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18">
+        <row r="4">
+          <cell r="D4" t="e">
+            <v>#VALUE!</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="19" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="表紙"/>
+      <sheetName val="運用状況"/>
+      <sheetName val="ローン完済までの収支シミュレーション"/>
+      <sheetName val="保有 or 売却　シミュレーション"/>
+      <sheetName val="譲渡税の計算"/>
+      <sheetName val="借り換えをした場合の比較2件同時"/>
+      <sheetName val="ローン計画書"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="約定"/>
+      <sheetName val="依頼"/>
+      <sheetName val="代理"/>
+      <sheetName val="依頼 (販売用）"/>
+      <sheetName val="委任"/>
+      <sheetName val="ＦＪ・スカイコート用委任"/>
+      <sheetName val="プレサンス委任"/>
+      <sheetName val="賃貸"/>
+      <sheetName val="保解"/>
+      <sheetName val="代解"/>
+      <sheetName val="振込"/>
+      <sheetName val="預証"/>
+      <sheetName val="注意事項書_"/>
+      <sheetName val="手付0円確認書"/>
+      <sheetName val="（売）一般媒介"/>
+      <sheetName val="（売）専任媒介 "/>
+      <sheetName val="項目"/>
+      <sheetName val="契約書A3版"/>
+      <sheetName val="37条書面"/>
+      <sheetName val="ベルテックス特約"/>
+      <sheetName val="契約書"/>
+      <sheetName val="設備表"/>
+      <sheetName val="一般"/>
+      <sheetName val="一般 (先行契約用)"/>
+      <sheetName val="表紙"/>
+      <sheetName val="【売】精算"/>
+      <sheetName val="【買】精算"/>
+      <sheetName val="【売】印"/>
+      <sheetName val="【買】印"/>
+      <sheetName val="【売】手"/>
+      <sheetName val="【買】手"/>
+      <sheetName val="【買】コンサル"/>
+      <sheetName val="手付"/>
+      <sheetName val="残金"/>
+      <sheetName val="精算"/>
+      <sheetName val="【買】家賃精算"/>
+      <sheetName val="【売】預証 "/>
+      <sheetName val="【買】預証"/>
+      <sheetName val="（買）一般媒介"/>
+      <sheetName val="（買）専任媒介"/>
+      <sheetName val="【買】約定"/>
+      <sheetName val="コンサル契約書"/>
+      <sheetName val="コンサル（ベルテックス）"/>
+      <sheetName val="合意書_"/>
+      <sheetName val="当変"/>
+      <sheetName val="改正対応覚書"/>
+      <sheetName val="覚書"/>
+      <sheetName val="覚書 (ロイズ四為)"/>
+      <sheetName val="取引台帳"/>
+      <sheetName val="取引台帳 (2)"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+      <sheetData sheetId="42" refreshError="1"/>
+      <sheetData sheetId="43" refreshError="1"/>
+      <sheetData sheetId="44" refreshError="1"/>
+      <sheetData sheetId="45" refreshError="1"/>
+      <sheetData sheetId="46" refreshError="1"/>
+      <sheetData sheetId="47" refreshError="1"/>
+      <sheetData sheetId="48" refreshError="1"/>
+      <sheetData sheetId="49" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1976,858 +4310,5729 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EE49FEF-859A-2846-9065-2C96E9D17D94}">
-  <dimension ref="A1:N30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{193F2714-3A35-A84E-AAE5-9B9617B0457C}">
+  <sheetPr>
+    <tabColor rgb="FF006600"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:CW65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="16" customWidth="1"/>
+    <col min="3" max="26" width="13.140625" style="8" customWidth="1"/>
+    <col min="27" max="27" width="7.5703125" style="8" customWidth="1"/>
+    <col min="28" max="48" width="10.140625" style="8" customWidth="1"/>
+    <col min="49" max="49" width="7.5703125" style="8"/>
+    <col min="50" max="50" width="16.5703125" style="8" customWidth="1"/>
+    <col min="51" max="100" width="30.5703125" style="8" customWidth="1"/>
+    <col min="101" max="16384" width="7.5703125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33">
-      <c r="A1" s="1">
+    <row r="1" spans="1:101" s="4" customFormat="1" ht="20.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" spans="1:101" ht="31.5" customHeight="1">
+      <c r="A2" s="5">
+        <f>[1]表紙!B18</f>
+        <v>0</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+    </row>
+    <row r="3" spans="1:101" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+    </row>
+    <row r="4" spans="1:101" ht="20.25" customHeight="1" thickTop="1">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="K4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="14"/>
+      <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
+      <c r="Q4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="14"/>
+      <c r="S4" s="14"/>
+      <c r="T4" s="14"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="AB4" s="15">
+        <f>MIN(C23,F23,I23,L23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:101" ht="20.25" customHeight="1">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" s="14"/>
+      <c r="S5" s="14"/>
+      <c r="T5" s="14"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="17"/>
+      <c r="W5" s="17"/>
+      <c r="AB5" s="8">
+        <f>YEAR(AB4)</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:101" ht="20.25" customHeight="1">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="17"/>
+      <c r="W6" s="17"/>
+      <c r="AW6" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AX6" s="20"/>
+      <c r="AY6" s="20"/>
+    </row>
+    <row r="7" spans="1:101" ht="27.5" customHeight="1">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22">
         <v>2026</v>
       </c>
-      <c r="B1" s="28">
+      <c r="C7" s="23">
         <f ca="1">TODAY()</f>
         <v>46276</v>
       </c>
-      <c r="C1" s="59"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="61"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24">
+        <f>YEAR(C23)</f>
+        <v>1900</v>
+      </c>
+      <c r="F7" s="25"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24">
+        <f>YEAR(F23)</f>
+        <v>1900</v>
+      </c>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="24">
+        <f>YEAR(I23)</f>
+        <v>1900</v>
+      </c>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="24">
+        <f>YEAR(L23)</f>
+        <v>1900</v>
+      </c>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="24">
+        <f>YEAR(O23)</f>
+        <v>1900</v>
+      </c>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26"/>
+      <c r="T7" s="24">
+        <f>YEAR(R23)</f>
+        <v>1900</v>
+      </c>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="24">
+        <f>YEAR(U23)</f>
+        <v>1900</v>
+      </c>
+      <c r="AW7" s="20"/>
+      <c r="AX7" s="20"/>
+      <c r="AY7" s="20"/>
     </row>
-    <row r="2" spans="1:14" ht="33">
-      <c r="A2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="4"/>
+    <row r="8" spans="1:101" ht="24" customHeight="1" thickBot="1">
+      <c r="A8" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="30">
+        <f>E7-C11</f>
+        <v>1900</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="30">
+        <f>H7-F11</f>
+        <v>1900</v>
+      </c>
+      <c r="H8" s="30"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="30">
+        <f>K7-I11</f>
+        <v>1900</v>
+      </c>
+      <c r="K8" s="30"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="30">
+        <f>N7-L11</f>
+        <v>1900</v>
+      </c>
+      <c r="N8" s="30"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="30">
+        <f>Q7-O11</f>
+        <v>1900</v>
+      </c>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="30">
+        <f>T7-R11</f>
+        <v>1900</v>
+      </c>
+      <c r="T8" s="30"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="30">
+        <f>W7-U11</f>
+        <v>1900</v>
+      </c>
+      <c r="W8" s="30"/>
+      <c r="AI8" s="33">
+        <v>35</v>
+      </c>
+      <c r="AJ8" s="34">
+        <v>80</v>
+      </c>
+      <c r="AK8" s="35">
+        <f>DATE(YEAR(C23)+AI8,MONTH(C23),DAY(C23))</f>
+        <v>12784</v>
+      </c>
+      <c r="AL8" s="35">
+        <f>DATE(YEAR(F23)+AI8,MONTH(F23),DAY(F23))</f>
+        <v>12784</v>
+      </c>
+      <c r="AM8" s="35">
+        <f>DATE(YEAR(I23)+AI8,MONTH(I23),DAY(I23))</f>
+        <v>12784</v>
+      </c>
+      <c r="AN8" s="35">
+        <f>DATE(YEAR(L23)+AI8,MONTH(L23),DAY(L23))</f>
+        <v>12784</v>
+      </c>
+      <c r="AW8" s="20"/>
+      <c r="AX8" s="20"/>
+      <c r="AY8" s="20"/>
+      <c r="AZ8" s="36"/>
     </row>
-    <row r="3" spans="1:14" ht="21" thickBot="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7" t="str">
-        <f>IF(C1="","",$A$1-C3)</f>
+    <row r="9" spans="1:101" s="41" customFormat="1" ht="31" customHeight="1">
+      <c r="A9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="39"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="39"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="40"/>
+      <c r="AI9" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ9" s="42"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="35"/>
+      <c r="AM9" s="35"/>
+      <c r="AN9" s="35"/>
+      <c r="AW9" s="20"/>
+      <c r="AX9" s="20"/>
+      <c r="AY9" s="20"/>
+      <c r="AZ9" s="8"/>
+      <c r="BA9" s="8"/>
+      <c r="BB9" s="8"/>
+      <c r="BC9" s="8"/>
+      <c r="BD9" s="8"/>
+      <c r="BE9" s="8"/>
+      <c r="BF9" s="8"/>
+      <c r="BG9" s="8"/>
+      <c r="BH9" s="8"/>
+      <c r="BI9" s="8"/>
+      <c r="BJ9" s="8"/>
+      <c r="BK9" s="8"/>
+      <c r="BL9" s="8"/>
+      <c r="BM9" s="8"/>
+      <c r="BN9" s="8"/>
+      <c r="BO9" s="8"/>
+      <c r="BP9" s="8"/>
+      <c r="BQ9" s="8"/>
+      <c r="BR9" s="8"/>
+      <c r="BS9" s="8"/>
+      <c r="BT9" s="8"/>
+      <c r="BU9" s="8"/>
+      <c r="BV9" s="8"/>
+      <c r="BW9" s="8"/>
+      <c r="BX9" s="8"/>
+      <c r="BY9" s="8"/>
+      <c r="BZ9" s="8"/>
+      <c r="CA9" s="8"/>
+      <c r="CB9" s="8"/>
+      <c r="CC9" s="8"/>
+      <c r="CD9" s="8"/>
+      <c r="CE9" s="8"/>
+      <c r="CF9" s="8"/>
+      <c r="CG9" s="8"/>
+      <c r="CH9" s="8"/>
+      <c r="CI9" s="8"/>
+      <c r="CJ9" s="8"/>
+      <c r="CK9" s="8"/>
+      <c r="CL9" s="8"/>
+      <c r="CM9" s="8"/>
+      <c r="CN9" s="8"/>
+      <c r="CO9" s="8"/>
+      <c r="CP9" s="8"/>
+      <c r="CQ9" s="8"/>
+      <c r="CR9" s="8"/>
+      <c r="CS9" s="8"/>
+      <c r="CT9" s="8"/>
+      <c r="CU9" s="8"/>
+      <c r="CV9" s="8"/>
+      <c r="CW9" s="8"/>
+    </row>
+    <row r="10" spans="1:101" ht="21" customHeight="1">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="45"/>
+      <c r="N10" s="46"/>
+      <c r="O10" s="44"/>
+      <c r="P10" s="45"/>
+      <c r="Q10" s="46"/>
+      <c r="R10" s="44"/>
+      <c r="S10" s="45"/>
+      <c r="T10" s="46"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="46"/>
+      <c r="AI10" s="42" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ10" s="42"/>
+      <c r="AK10" s="47">
+        <f>AJ8-AB16</f>
+        <v>206</v>
+      </c>
+      <c r="AW10" s="20"/>
+      <c r="AX10" s="20"/>
+      <c r="AY10" s="20"/>
+    </row>
+    <row r="11" spans="1:101" ht="26.25" customHeight="1" thickBot="1">
+      <c r="A11" s="48"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="50" t="str">
+        <f>IF(C9="","",$B$7-C11)</f>
         <v/>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7" t="str">
-        <f>IF(F1="","",$A$1-F3)</f>
+      <c r="E11" s="51"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="50" t="str">
+        <f>IF(F9="","",$B$7-F11)</f>
         <v/>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="7" t="str">
-        <f>IF(I1="","",$A$1-I3)</f>
+      <c r="H11" s="51"/>
+      <c r="I11" s="49"/>
+      <c r="J11" s="50" t="str">
+        <f>IF(I9="","",$B$7-I11)</f>
         <v/>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="7" t="str">
-        <f>IF(L1="","",$A$1-L3)</f>
+      <c r="K11" s="51"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="50" t="str">
+        <f>IF(L9="","",$B$7-L11)</f>
         <v/>
       </c>
-      <c r="N3" s="8"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="50" t="str">
+        <f>IF(O9="","",$B$7-O11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="50" t="str">
+        <f>IF(R9="","",$B$7-R11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="51"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="50" t="str">
+        <f>IF(U9="","",$B$7-U11)</f>
+        <v/>
+      </c>
+      <c r="W11" s="51"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AI11" s="42"/>
+      <c r="AJ11" s="42"/>
+      <c r="AK11" s="47"/>
+      <c r="AM11" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="AW11" s="20"/>
+      <c r="AX11" s="20"/>
+      <c r="AY11" s="20"/>
     </row>
-    <row r="4" spans="1:14" ht="60" customHeight="1" thickBot="1">
-      <c r="A4" s="104" t="s">
+    <row r="12" spans="1:101" ht="60" customHeight="1" thickBot="1">
+      <c r="A12" s="286" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B12" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="62"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="64"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
+      <c r="K12" s="56"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="57"/>
+      <c r="AW12" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX12" s="58"/>
+      <c r="AY12" s="59">
+        <f>2022+1</f>
+        <v>2023</v>
+      </c>
+      <c r="AZ12" s="59">
+        <f>AY12+1</f>
+        <v>2024</v>
+      </c>
+      <c r="BA12" s="59">
+        <f t="shared" ref="BA12" si="0">AZ12+1</f>
+        <v>2025</v>
+      </c>
+      <c r="BB12" s="59">
+        <f t="shared" ref="BB12" si="1">BA12+1</f>
+        <v>2026</v>
+      </c>
+      <c r="BC12" s="59">
+        <f t="shared" ref="BC12" si="2">BB12+1</f>
+        <v>2027</v>
+      </c>
+      <c r="BD12" s="59">
+        <f t="shared" ref="BD12" si="3">BC12+1</f>
+        <v>2028</v>
+      </c>
+      <c r="BE12" s="59">
+        <f t="shared" ref="BE12" si="4">BD12+1</f>
+        <v>2029</v>
+      </c>
+      <c r="BF12" s="59">
+        <f t="shared" ref="BF12" si="5">BE12+1</f>
+        <v>2030</v>
+      </c>
+      <c r="BG12" s="59">
+        <f t="shared" ref="BG12" si="6">BF12+1</f>
+        <v>2031</v>
+      </c>
+      <c r="BH12" s="59">
+        <f t="shared" ref="BH12" si="7">BG12+1</f>
+        <v>2032</v>
+      </c>
+      <c r="BI12" s="59">
+        <f t="shared" ref="BI12" si="8">BH12+1</f>
+        <v>2033</v>
+      </c>
+      <c r="BJ12" s="59">
+        <f t="shared" ref="BJ12" si="9">BI12+1</f>
+        <v>2034</v>
+      </c>
+      <c r="BK12" s="59">
+        <f t="shared" ref="BK12" si="10">BJ12+1</f>
+        <v>2035</v>
+      </c>
+      <c r="BL12" s="59">
+        <f t="shared" ref="BL12" si="11">BK12+1</f>
+        <v>2036</v>
+      </c>
+      <c r="BM12" s="59">
+        <f t="shared" ref="BM12" si="12">BL12+1</f>
+        <v>2037</v>
+      </c>
+      <c r="BN12" s="59">
+        <f t="shared" ref="BN12" si="13">BM12+1</f>
+        <v>2038</v>
+      </c>
+      <c r="BO12" s="59">
+        <f t="shared" ref="BO12" si="14">BN12+1</f>
+        <v>2039</v>
+      </c>
+      <c r="BP12" s="59">
+        <f t="shared" ref="BP12" si="15">BO12+1</f>
+        <v>2040</v>
+      </c>
+      <c r="BQ12" s="59">
+        <f t="shared" ref="BQ12" si="16">BP12+1</f>
+        <v>2041</v>
+      </c>
+      <c r="BR12" s="59">
+        <f t="shared" ref="BR12" si="17">BQ12+1</f>
+        <v>2042</v>
+      </c>
+      <c r="BS12" s="59">
+        <f t="shared" ref="BS12" si="18">BR12+1</f>
+        <v>2043</v>
+      </c>
+      <c r="BT12" s="59">
+        <f t="shared" ref="BT12" si="19">BS12+1</f>
+        <v>2044</v>
+      </c>
+      <c r="BU12" s="59">
+        <f t="shared" ref="BU12" si="20">BT12+1</f>
+        <v>2045</v>
+      </c>
+      <c r="BV12" s="59">
+        <f t="shared" ref="BV12" si="21">BU12+1</f>
+        <v>2046</v>
+      </c>
+      <c r="BW12" s="59">
+        <f t="shared" ref="BW12" si="22">BV12+1</f>
+        <v>2047</v>
+      </c>
+      <c r="BX12" s="59">
+        <f t="shared" ref="BX12" si="23">BW12+1</f>
+        <v>2048</v>
+      </c>
+      <c r="BY12" s="59">
+        <f t="shared" ref="BY12" si="24">BX12+1</f>
+        <v>2049</v>
+      </c>
+      <c r="BZ12" s="59">
+        <f t="shared" ref="BZ12" si="25">BY12+1</f>
+        <v>2050</v>
+      </c>
+      <c r="CA12" s="59">
+        <f t="shared" ref="CA12" si="26">BZ12+1</f>
+        <v>2051</v>
+      </c>
+      <c r="CB12" s="59">
+        <f t="shared" ref="CB12" si="27">CA12+1</f>
+        <v>2052</v>
+      </c>
+      <c r="CC12" s="59">
+        <f t="shared" ref="CC12" si="28">CB12+1</f>
+        <v>2053</v>
+      </c>
+      <c r="CD12" s="59">
+        <f t="shared" ref="CD12" si="29">CC12+1</f>
+        <v>2054</v>
+      </c>
+      <c r="CE12" s="59">
+        <f t="shared" ref="CE12" si="30">CD12+1</f>
+        <v>2055</v>
+      </c>
+      <c r="CF12" s="59">
+        <f t="shared" ref="CF12" si="31">CE12+1</f>
+        <v>2056</v>
+      </c>
+      <c r="CG12" s="59">
+        <f t="shared" ref="CG12" si="32">CF12+1</f>
+        <v>2057</v>
+      </c>
+      <c r="CH12" s="59">
+        <f t="shared" ref="CH12" si="33">CG12+1</f>
+        <v>2058</v>
+      </c>
+      <c r="CI12" s="59">
+        <f t="shared" ref="CI12" si="34">CH12+1</f>
+        <v>2059</v>
+      </c>
+      <c r="CJ12" s="59">
+        <f t="shared" ref="CJ12" si="35">CI12+1</f>
+        <v>2060</v>
+      </c>
+      <c r="CK12" s="59">
+        <f t="shared" ref="CK12" si="36">CJ12+1</f>
+        <v>2061</v>
+      </c>
+      <c r="CL12" s="59">
+        <f t="shared" ref="CL12" si="37">CK12+1</f>
+        <v>2062</v>
+      </c>
+      <c r="CM12" s="59">
+        <f t="shared" ref="CM12" si="38">CL12+1</f>
+        <v>2063</v>
+      </c>
+      <c r="CN12" s="59">
+        <f t="shared" ref="CN12" si="39">CM12+1</f>
+        <v>2064</v>
+      </c>
+      <c r="CO12" s="59">
+        <f t="shared" ref="CO12" si="40">CN12+1</f>
+        <v>2065</v>
+      </c>
+      <c r="CP12" s="59">
+        <f t="shared" ref="CP12" si="41">CO12+1</f>
+        <v>2066</v>
+      </c>
+      <c r="CQ12" s="59">
+        <f t="shared" ref="CQ12" si="42">CP12+1</f>
+        <v>2067</v>
+      </c>
+      <c r="CR12" s="59">
+        <f t="shared" ref="CR12" si="43">CQ12+1</f>
+        <v>2068</v>
+      </c>
+      <c r="CS12" s="59">
+        <f t="shared" ref="CS12" si="44">CR12+1</f>
+        <v>2069</v>
+      </c>
+      <c r="CT12" s="59">
+        <f t="shared" ref="CT12" si="45">CS12+1</f>
+        <v>2070</v>
+      </c>
+      <c r="CU12" s="59">
+        <f t="shared" ref="CU12" si="46">CT12+1</f>
+        <v>2071</v>
+      </c>
+      <c r="CV12" s="59">
+        <f t="shared" ref="CV12" si="47">CU12+1</f>
+        <v>2072</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="60" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A5" s="95"/>
-      <c r="B5" s="9" t="s">
+    <row r="13" spans="1:101" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A13" s="70"/>
+      <c r="B13" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="62"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
-      <c r="L5" s="62"/>
-      <c r="M5" s="63"/>
-      <c r="N5" s="64"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="55"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="55"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="57"/>
+      <c r="AW13" s="58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX13" s="58"/>
+      <c r="AY13" s="59">
+        <f>2022+1</f>
+        <v>2023</v>
+      </c>
+      <c r="AZ13" s="59">
+        <f>AY13+1</f>
+        <v>2024</v>
+      </c>
+      <c r="BA13" s="59">
+        <f t="shared" ref="BA13:CV13" si="48">AZ13+1</f>
+        <v>2025</v>
+      </c>
+      <c r="BB13" s="59">
+        <f t="shared" si="48"/>
+        <v>2026</v>
+      </c>
+      <c r="BC13" s="59">
+        <f t="shared" si="48"/>
+        <v>2027</v>
+      </c>
+      <c r="BD13" s="59">
+        <f t="shared" si="48"/>
+        <v>2028</v>
+      </c>
+      <c r="BE13" s="59">
+        <f t="shared" si="48"/>
+        <v>2029</v>
+      </c>
+      <c r="BF13" s="59">
+        <f t="shared" si="48"/>
+        <v>2030</v>
+      </c>
+      <c r="BG13" s="59">
+        <f t="shared" si="48"/>
+        <v>2031</v>
+      </c>
+      <c r="BH13" s="59">
+        <f t="shared" si="48"/>
+        <v>2032</v>
+      </c>
+      <c r="BI13" s="59">
+        <f t="shared" si="48"/>
+        <v>2033</v>
+      </c>
+      <c r="BJ13" s="59">
+        <f t="shared" si="48"/>
+        <v>2034</v>
+      </c>
+      <c r="BK13" s="59">
+        <f t="shared" si="48"/>
+        <v>2035</v>
+      </c>
+      <c r="BL13" s="59">
+        <f t="shared" si="48"/>
+        <v>2036</v>
+      </c>
+      <c r="BM13" s="59">
+        <f t="shared" si="48"/>
+        <v>2037</v>
+      </c>
+      <c r="BN13" s="59">
+        <f t="shared" si="48"/>
+        <v>2038</v>
+      </c>
+      <c r="BO13" s="59">
+        <f t="shared" si="48"/>
+        <v>2039</v>
+      </c>
+      <c r="BP13" s="59">
+        <f t="shared" si="48"/>
+        <v>2040</v>
+      </c>
+      <c r="BQ13" s="59">
+        <f t="shared" si="48"/>
+        <v>2041</v>
+      </c>
+      <c r="BR13" s="59">
+        <f t="shared" si="48"/>
+        <v>2042</v>
+      </c>
+      <c r="BS13" s="59">
+        <f t="shared" si="48"/>
+        <v>2043</v>
+      </c>
+      <c r="BT13" s="59">
+        <f t="shared" si="48"/>
+        <v>2044</v>
+      </c>
+      <c r="BU13" s="59">
+        <f t="shared" si="48"/>
+        <v>2045</v>
+      </c>
+      <c r="BV13" s="59">
+        <f t="shared" si="48"/>
+        <v>2046</v>
+      </c>
+      <c r="BW13" s="59">
+        <f t="shared" si="48"/>
+        <v>2047</v>
+      </c>
+      <c r="BX13" s="59">
+        <f t="shared" si="48"/>
+        <v>2048</v>
+      </c>
+      <c r="BY13" s="59">
+        <f t="shared" si="48"/>
+        <v>2049</v>
+      </c>
+      <c r="BZ13" s="59">
+        <f t="shared" si="48"/>
+        <v>2050</v>
+      </c>
+      <c r="CA13" s="59">
+        <f t="shared" si="48"/>
+        <v>2051</v>
+      </c>
+      <c r="CB13" s="59">
+        <f t="shared" si="48"/>
+        <v>2052</v>
+      </c>
+      <c r="CC13" s="59">
+        <f t="shared" si="48"/>
+        <v>2053</v>
+      </c>
+      <c r="CD13" s="59">
+        <f t="shared" si="48"/>
+        <v>2054</v>
+      </c>
+      <c r="CE13" s="59">
+        <f t="shared" si="48"/>
+        <v>2055</v>
+      </c>
+      <c r="CF13" s="59">
+        <f t="shared" si="48"/>
+        <v>2056</v>
+      </c>
+      <c r="CG13" s="59">
+        <f t="shared" si="48"/>
+        <v>2057</v>
+      </c>
+      <c r="CH13" s="59">
+        <f t="shared" si="48"/>
+        <v>2058</v>
+      </c>
+      <c r="CI13" s="59">
+        <f t="shared" si="48"/>
+        <v>2059</v>
+      </c>
+      <c r="CJ13" s="59">
+        <f t="shared" si="48"/>
+        <v>2060</v>
+      </c>
+      <c r="CK13" s="59">
+        <f t="shared" si="48"/>
+        <v>2061</v>
+      </c>
+      <c r="CL13" s="59">
+        <f t="shared" si="48"/>
+        <v>2062</v>
+      </c>
+      <c r="CM13" s="59">
+        <f t="shared" si="48"/>
+        <v>2063</v>
+      </c>
+      <c r="CN13" s="59">
+        <f t="shared" si="48"/>
+        <v>2064</v>
+      </c>
+      <c r="CO13" s="59">
+        <f t="shared" si="48"/>
+        <v>2065</v>
+      </c>
+      <c r="CP13" s="59">
+        <f t="shared" si="48"/>
+        <v>2066</v>
+      </c>
+      <c r="CQ13" s="59">
+        <f t="shared" si="48"/>
+        <v>2067</v>
+      </c>
+      <c r="CR13" s="59">
+        <f t="shared" si="48"/>
+        <v>2068</v>
+      </c>
+      <c r="CS13" s="59">
+        <f t="shared" si="48"/>
+        <v>2069</v>
+      </c>
+      <c r="CT13" s="59">
+        <f t="shared" si="48"/>
+        <v>2070</v>
+      </c>
+      <c r="CU13" s="59">
+        <f t="shared" si="48"/>
+        <v>2071</v>
+      </c>
+      <c r="CV13" s="59">
+        <f t="shared" si="48"/>
+        <v>2072</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" ht="21" thickTop="1">
-      <c r="A6" s="94" t="s">
+    <row r="14" spans="1:101" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A14" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B14" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
-      <c r="L6" s="65"/>
-      <c r="M6" s="65"/>
-      <c r="N6" s="65"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
+      <c r="F14" s="62"/>
+      <c r="G14" s="62"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="62"/>
+      <c r="J14" s="62"/>
+      <c r="K14" s="62"/>
+      <c r="L14" s="62"/>
+      <c r="M14" s="62"/>
+      <c r="N14" s="62"/>
+      <c r="O14" s="62"/>
+      <c r="P14" s="62"/>
+      <c r="Q14" s="62"/>
+      <c r="R14" s="62"/>
+      <c r="S14" s="62"/>
+      <c r="T14" s="62"/>
+      <c r="U14" s="62"/>
+      <c r="V14" s="62"/>
+      <c r="W14" s="62"/>
+      <c r="AB14" s="63" t="s">
+        <v>40</v>
+      </c>
+      <c r="AC14" s="64"/>
+      <c r="AD14" s="64"/>
+      <c r="AE14" s="64"/>
+      <c r="AF14" s="64"/>
+      <c r="AG14" s="64"/>
+      <c r="AH14" s="64"/>
+      <c r="AI14" s="64"/>
+      <c r="AJ14" s="64"/>
+      <c r="AK14" s="64"/>
+      <c r="AL14" s="65"/>
+      <c r="AW14" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AX14" s="67"/>
+      <c r="AY14" s="68">
+        <v>1</v>
+      </c>
+      <c r="AZ14" s="68">
+        <v>2</v>
+      </c>
+      <c r="BA14" s="68">
+        <v>3</v>
+      </c>
+      <c r="BB14" s="69">
+        <v>4</v>
+      </c>
+      <c r="BC14" s="68">
+        <v>5</v>
+      </c>
+      <c r="BD14" s="68">
+        <v>6</v>
+      </c>
+      <c r="BE14" s="68">
+        <v>7</v>
+      </c>
+      <c r="BF14" s="68">
+        <v>8</v>
+      </c>
+      <c r="BG14" s="68">
+        <v>9</v>
+      </c>
+      <c r="BH14" s="68">
+        <v>10</v>
+      </c>
+      <c r="BI14" s="68">
+        <v>11</v>
+      </c>
+      <c r="BJ14" s="68">
+        <v>12</v>
+      </c>
+      <c r="BK14" s="69">
+        <v>13</v>
+      </c>
+      <c r="BL14" s="68">
+        <v>14</v>
+      </c>
+      <c r="BM14" s="68">
+        <v>15</v>
+      </c>
+      <c r="BN14" s="68">
+        <v>16</v>
+      </c>
+      <c r="BO14" s="68">
+        <v>17</v>
+      </c>
+      <c r="BP14" s="68">
+        <v>18</v>
+      </c>
+      <c r="BQ14" s="68">
+        <v>19</v>
+      </c>
+      <c r="BR14" s="68">
+        <v>20</v>
+      </c>
+      <c r="BS14" s="68">
+        <v>21</v>
+      </c>
+      <c r="BT14" s="68">
+        <v>22</v>
+      </c>
+      <c r="BU14" s="68">
+        <v>23</v>
+      </c>
+      <c r="BV14" s="68">
+        <v>24</v>
+      </c>
+      <c r="BW14" s="68">
+        <v>25</v>
+      </c>
+      <c r="BX14" s="68">
+        <v>26</v>
+      </c>
+      <c r="BY14" s="68">
+        <v>27</v>
+      </c>
+      <c r="BZ14" s="68">
+        <v>28</v>
+      </c>
+      <c r="CA14" s="68">
+        <v>29</v>
+      </c>
+      <c r="CB14" s="68">
+        <v>30</v>
+      </c>
+      <c r="CC14" s="69">
+        <v>31</v>
+      </c>
+      <c r="CD14" s="68">
+        <v>32</v>
+      </c>
+      <c r="CE14" s="68">
+        <v>33</v>
+      </c>
+      <c r="CF14" s="68">
+        <v>34</v>
+      </c>
+      <c r="CG14" s="69">
+        <v>35</v>
+      </c>
+      <c r="CH14" s="69">
+        <v>36</v>
+      </c>
+      <c r="CI14" s="69">
+        <v>37</v>
+      </c>
+      <c r="CJ14" s="69">
+        <v>38</v>
+      </c>
+      <c r="CK14" s="69">
+        <v>39</v>
+      </c>
+      <c r="CL14" s="69">
+        <v>40</v>
+      </c>
+      <c r="CM14" s="69">
+        <v>41</v>
+      </c>
+      <c r="CN14" s="69">
+        <v>42</v>
+      </c>
+      <c r="CO14" s="69">
+        <v>43</v>
+      </c>
+      <c r="CP14" s="69">
+        <v>44</v>
+      </c>
+      <c r="CQ14" s="69">
+        <v>45</v>
+      </c>
+      <c r="CR14" s="69">
+        <v>46</v>
+      </c>
+      <c r="CS14" s="69">
+        <v>47</v>
+      </c>
+      <c r="CT14" s="69">
+        <v>48</v>
+      </c>
+      <c r="CU14" s="69">
+        <v>49</v>
+      </c>
+      <c r="CV14" s="69">
+        <v>50</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" ht="21" thickBot="1">
-      <c r="A7" s="95"/>
-      <c r="B7" s="11" t="s">
+    <row r="15" spans="1:101" ht="60" customHeight="1" thickBot="1">
+      <c r="A15" s="70"/>
+      <c r="B15" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="66"/>
-      <c r="L7" s="66"/>
-      <c r="M7" s="66"/>
-      <c r="N7" s="66"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="72"/>
+      <c r="G15" s="72"/>
+      <c r="H15" s="72"/>
+      <c r="I15" s="72"/>
+      <c r="J15" s="72"/>
+      <c r="K15" s="72"/>
+      <c r="L15" s="72"/>
+      <c r="M15" s="72"/>
+      <c r="N15" s="72"/>
+      <c r="O15" s="72"/>
+      <c r="P15" s="72"/>
+      <c r="Q15" s="72"/>
+      <c r="R15" s="72"/>
+      <c r="S15" s="72"/>
+      <c r="T15" s="72"/>
+      <c r="U15" s="72"/>
+      <c r="V15" s="72"/>
+      <c r="W15" s="72"/>
+      <c r="AB15" s="73" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC15" s="74"/>
+      <c r="AD15" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE15" s="76" t="s">
+        <v>44</v>
+      </c>
+      <c r="AF15" s="76"/>
+      <c r="AG15" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH15" s="76" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI15" s="76"/>
+      <c r="AJ15" s="75" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK15" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="AL15" s="77"/>
+      <c r="AW15" s="78" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX15" s="79"/>
+      <c r="AY15" s="80">
+        <f>AE16</f>
+        <v>0</v>
+      </c>
+      <c r="AZ15" s="80">
+        <f>AY15+1</f>
+        <v>1</v>
+      </c>
+      <c r="BA15" s="80">
+        <f t="shared" ref="BA15:BP18" si="49">AZ15+1</f>
+        <v>2</v>
+      </c>
+      <c r="BB15" s="81">
+        <f t="shared" si="49"/>
+        <v>3</v>
+      </c>
+      <c r="BC15" s="80">
+        <f t="shared" si="49"/>
+        <v>4</v>
+      </c>
+      <c r="BD15" s="80">
+        <f t="shared" si="49"/>
+        <v>5</v>
+      </c>
+      <c r="BE15" s="80">
+        <f t="shared" si="49"/>
+        <v>6</v>
+      </c>
+      <c r="BF15" s="80">
+        <f t="shared" si="49"/>
+        <v>7</v>
+      </c>
+      <c r="BG15" s="80">
+        <f t="shared" si="49"/>
+        <v>8</v>
+      </c>
+      <c r="BH15" s="80">
+        <f t="shared" si="49"/>
+        <v>9</v>
+      </c>
+      <c r="BI15" s="80">
+        <f t="shared" si="49"/>
+        <v>10</v>
+      </c>
+      <c r="BJ15" s="80">
+        <f t="shared" si="49"/>
+        <v>11</v>
+      </c>
+      <c r="BK15" s="81">
+        <f t="shared" si="49"/>
+        <v>12</v>
+      </c>
+      <c r="BL15" s="80">
+        <f t="shared" si="49"/>
+        <v>13</v>
+      </c>
+      <c r="BM15" s="80">
+        <f t="shared" si="49"/>
+        <v>14</v>
+      </c>
+      <c r="BN15" s="80">
+        <f t="shared" si="49"/>
+        <v>15</v>
+      </c>
+      <c r="BO15" s="80">
+        <f t="shared" si="49"/>
+        <v>16</v>
+      </c>
+      <c r="BP15" s="80">
+        <f t="shared" si="49"/>
+        <v>17</v>
+      </c>
+      <c r="BQ15" s="80">
+        <f t="shared" ref="BQ15:CF18" si="50">BP15+1</f>
+        <v>18</v>
+      </c>
+      <c r="BR15" s="80">
+        <f t="shared" si="50"/>
+        <v>19</v>
+      </c>
+      <c r="BS15" s="80">
+        <f t="shared" si="50"/>
+        <v>20</v>
+      </c>
+      <c r="BT15" s="80">
+        <f t="shared" si="50"/>
+        <v>21</v>
+      </c>
+      <c r="BU15" s="80">
+        <f t="shared" si="50"/>
+        <v>22</v>
+      </c>
+      <c r="BV15" s="80">
+        <f t="shared" si="50"/>
+        <v>23</v>
+      </c>
+      <c r="BW15" s="80">
+        <f t="shared" si="50"/>
+        <v>24</v>
+      </c>
+      <c r="BX15" s="80">
+        <f t="shared" si="50"/>
+        <v>25</v>
+      </c>
+      <c r="BY15" s="80">
+        <f t="shared" si="50"/>
+        <v>26</v>
+      </c>
+      <c r="BZ15" s="80">
+        <f t="shared" si="50"/>
+        <v>27</v>
+      </c>
+      <c r="CA15" s="80">
+        <f t="shared" si="50"/>
+        <v>28</v>
+      </c>
+      <c r="CB15" s="80">
+        <f t="shared" si="50"/>
+        <v>29</v>
+      </c>
+      <c r="CC15" s="81">
+        <f t="shared" si="50"/>
+        <v>30</v>
+      </c>
+      <c r="CD15" s="80">
+        <f t="shared" si="50"/>
+        <v>31</v>
+      </c>
+      <c r="CE15" s="80">
+        <f t="shared" si="50"/>
+        <v>32</v>
+      </c>
+      <c r="CF15" s="80">
+        <f t="shared" si="50"/>
+        <v>33</v>
+      </c>
+      <c r="CG15" s="81">
+        <f t="shared" ref="CG15:CV18" si="51">CF15+1</f>
+        <v>34</v>
+      </c>
+      <c r="CH15" s="81">
+        <f t="shared" si="51"/>
+        <v>35</v>
+      </c>
+      <c r="CI15" s="81">
+        <f t="shared" si="51"/>
+        <v>36</v>
+      </c>
+      <c r="CJ15" s="81">
+        <f t="shared" si="51"/>
+        <v>37</v>
+      </c>
+      <c r="CK15" s="81">
+        <f t="shared" si="51"/>
+        <v>38</v>
+      </c>
+      <c r="CL15" s="81">
+        <f t="shared" si="51"/>
+        <v>39</v>
+      </c>
+      <c r="CM15" s="81">
+        <f t="shared" si="51"/>
+        <v>40</v>
+      </c>
+      <c r="CN15" s="81">
+        <f t="shared" si="51"/>
+        <v>41</v>
+      </c>
+      <c r="CO15" s="81">
+        <f t="shared" si="51"/>
+        <v>42</v>
+      </c>
+      <c r="CP15" s="81">
+        <f t="shared" si="51"/>
+        <v>43</v>
+      </c>
+      <c r="CQ15" s="81">
+        <f t="shared" si="51"/>
+        <v>44</v>
+      </c>
+      <c r="CR15" s="81">
+        <f t="shared" si="51"/>
+        <v>45</v>
+      </c>
+      <c r="CS15" s="81">
+        <f t="shared" si="51"/>
+        <v>46</v>
+      </c>
+      <c r="CT15" s="81">
+        <f t="shared" si="51"/>
+        <v>47</v>
+      </c>
+      <c r="CU15" s="81">
+        <f t="shared" si="51"/>
+        <v>48</v>
+      </c>
+      <c r="CV15" s="81">
+        <f t="shared" si="51"/>
+        <v>49</v>
+      </c>
     </row>
-    <row r="8" spans="1:14" ht="58" customHeight="1" thickTop="1">
-      <c r="A8" s="94" t="s">
+    <row r="16" spans="1:101" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A16" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B16" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="69"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="69"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="69"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="85"/>
+      <c r="F16" s="83"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="85"/>
+      <c r="I16" s="83"/>
+      <c r="J16" s="84"/>
+      <c r="K16" s="85"/>
+      <c r="L16" s="83"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="85"/>
+      <c r="R16" s="83"/>
+      <c r="S16" s="84"/>
+      <c r="T16" s="85"/>
+      <c r="U16" s="83"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="85"/>
+      <c r="AB16" s="86">
+        <f>IFERROR(AE16-AD16,"")</f>
+        <v>-126</v>
+      </c>
+      <c r="AC16" s="87"/>
+      <c r="AD16" s="88">
+        <f>AE17-AB17</f>
+        <v>126</v>
+      </c>
+      <c r="AE16" s="89"/>
+      <c r="AF16" s="90"/>
+      <c r="AG16" s="91">
+        <f>AH16-AE16</f>
+        <v>0</v>
+      </c>
+      <c r="AH16" s="89"/>
+      <c r="AI16" s="90"/>
+      <c r="AJ16" s="91">
+        <f>AE18-AG16</f>
+        <v>0</v>
+      </c>
+      <c r="AK16" s="92">
+        <f>AE16+AE18</f>
+        <v>0</v>
+      </c>
+      <c r="AL16" s="93"/>
+      <c r="AW16" s="78"/>
+      <c r="AX16" s="79"/>
+      <c r="AY16" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="AZ16" s="80" t="e">
+        <f>AY16+1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BA16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BB16" s="81" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BC16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BD16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BE16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BF16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BG16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BH16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BI16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BJ16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BK16" s="81" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BM16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BN16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BO16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BP16" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BQ16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BS16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BU16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BV16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BW16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BX16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BY16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BZ16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CA16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CB16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CC16" s="81" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CD16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CE16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CF16" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CG16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CH16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CI16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CJ16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CK16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CL16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CM16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CN16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CO16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CP16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CQ16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CR16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CS16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CT16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CU16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CV16" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
-    <row r="9" spans="1:14" ht="58" customHeight="1">
-      <c r="A9" s="94"/>
-      <c r="B9" s="13" t="s">
+    <row r="17" spans="1:100" ht="60" customHeight="1" thickBot="1">
+      <c r="A17" s="60"/>
+      <c r="B17" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="70"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="70"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="71"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="71"/>
-      <c r="N9" s="72"/>
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="97"/>
+      <c r="F17" s="95"/>
+      <c r="G17" s="96"/>
+      <c r="H17" s="97"/>
+      <c r="I17" s="95"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="95"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="97"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="97"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="96"/>
+      <c r="W17" s="97"/>
+      <c r="X17" s="98">
+        <f>SUM(C17:W17)</f>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="100"/>
+      <c r="AB17" s="101">
+        <f>AB5</f>
+        <v>1900</v>
+      </c>
+      <c r="AC17" s="102"/>
+      <c r="AD17" s="103"/>
+      <c r="AE17" s="104">
+        <f>B7</f>
+        <v>2026</v>
+      </c>
+      <c r="AF17" s="105"/>
+      <c r="AG17" s="106"/>
+      <c r="AH17" s="104">
+        <f>AE17+AG16</f>
+        <v>2026</v>
+      </c>
+      <c r="AI17" s="105"/>
+      <c r="AJ17" s="106"/>
+      <c r="AK17" s="104">
+        <f>AH17+AJ16</f>
+        <v>2026</v>
+      </c>
+      <c r="AL17" s="105"/>
+      <c r="AW17" s="78"/>
+      <c r="AX17" s="79"/>
+      <c r="AY17" s="80" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ17" s="80" t="e">
+        <f>AY17+1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BA17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BB17" s="81" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BC17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BD17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BE17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BF17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BG17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BH17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BI17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BJ17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BK17" s="81" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BM17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BN17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BO17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BP17" s="80" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BQ17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BS17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BU17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BV17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BW17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BX17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BY17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BZ17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CA17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CB17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CC17" s="81" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CD17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CE17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CF17" s="80" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CG17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CH17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CI17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CJ17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CK17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CL17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CM17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CN17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CO17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CP17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CQ17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CR17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CS17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CT17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CU17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CV17" s="81" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
     </row>
-    <row r="10" spans="1:14" ht="35" customHeight="1">
-      <c r="A10" s="94"/>
-      <c r="B10" s="96" t="s">
+    <row r="18" spans="1:100" ht="32.25" customHeight="1" thickBot="1">
+      <c r="A18" s="60"/>
+      <c r="B18" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="73" t="str">
-        <f>IF(C9&lt;&gt;"", DATE(YEAR($B$1), MONTH($B$1)+3, 1), "")</f>
+      <c r="C18" s="287"/>
+      <c r="D18" s="288"/>
+      <c r="E18" s="289"/>
+      <c r="F18" s="287"/>
+      <c r="G18" s="288"/>
+      <c r="H18" s="289"/>
+      <c r="I18" s="287"/>
+      <c r="J18" s="288"/>
+      <c r="K18" s="289"/>
+      <c r="L18" s="287"/>
+      <c r="M18" s="288"/>
+      <c r="N18" s="289"/>
+      <c r="O18" s="287"/>
+      <c r="P18" s="288"/>
+      <c r="Q18" s="289"/>
+      <c r="R18" s="287"/>
+      <c r="S18" s="288"/>
+      <c r="T18" s="289"/>
+      <c r="U18" s="287"/>
+      <c r="V18" s="288"/>
+      <c r="W18" s="289"/>
+      <c r="AE18" s="108">
+        <f>MAX([1]下落!C12:N12)</f>
+        <v>0</v>
+      </c>
+      <c r="AF18" s="108"/>
+      <c r="AG18" s="109"/>
+      <c r="AH18" s="109"/>
+      <c r="AI18" s="109"/>
+      <c r="AJ18" s="109"/>
+      <c r="AK18" s="109"/>
+      <c r="AL18" s="109"/>
+      <c r="AW18" s="110"/>
+      <c r="AX18" s="111"/>
+      <c r="AY18" s="112" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ18" s="112" t="e">
+        <f>AY18+1</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BA18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BB18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BC18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BD18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BE18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BF18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BG18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BH18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BI18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BJ18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BK18" s="113" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BL18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BM18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BN18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BO18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BP18" s="112" t="e">
+        <f t="shared" si="49"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BQ18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BR18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BS18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BT18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BU18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BV18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BW18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BX18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BY18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="BZ18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CA18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CB18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CC18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CD18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CE18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CF18" s="112" t="e">
+        <f t="shared" si="50"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CG18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CH18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CI18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CJ18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CK18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CL18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CM18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CN18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CO18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CP18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CQ18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CR18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CS18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CT18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CU18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="CV18" s="112" t="e">
+        <f t="shared" si="51"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:100" ht="60" customHeight="1" thickBot="1">
+      <c r="A19" s="60"/>
+      <c r="B19" s="114"/>
+      <c r="C19" s="115"/>
+      <c r="D19" s="116"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="116"/>
+      <c r="H19" s="117"/>
+      <c r="I19" s="115"/>
+      <c r="J19" s="116"/>
+      <c r="K19" s="117"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="116"/>
+      <c r="N19" s="117"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="116"/>
+      <c r="Q19" s="117"/>
+      <c r="R19" s="115"/>
+      <c r="S19" s="116"/>
+      <c r="T19" s="117"/>
+      <c r="U19" s="115"/>
+      <c r="V19" s="116"/>
+      <c r="W19" s="117"/>
+      <c r="X19" s="98">
+        <f>SUM(C19:W19)</f>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="99"/>
+      <c r="Z19" s="100"/>
+      <c r="AE19" s="109"/>
+      <c r="AF19" s="109"/>
+      <c r="AG19" s="109"/>
+      <c r="AH19" s="109"/>
+      <c r="AI19" s="109"/>
+      <c r="AJ19" s="109"/>
+      <c r="AK19" s="109"/>
+      <c r="AL19" s="109"/>
+      <c r="AW19" s="118"/>
+      <c r="AX19" s="119"/>
+      <c r="AY19" s="120"/>
+      <c r="AZ19" s="120"/>
+      <c r="BA19" s="120"/>
+      <c r="BB19" s="120"/>
+      <c r="BC19" s="120"/>
+      <c r="BD19" s="120"/>
+      <c r="BE19" s="120"/>
+      <c r="BF19" s="120"/>
+      <c r="BG19" s="120"/>
+      <c r="BH19" s="120"/>
+      <c r="BI19" s="120"/>
+      <c r="BJ19" s="120"/>
+      <c r="BK19" s="121"/>
+      <c r="BL19" s="120"/>
+      <c r="BM19" s="120"/>
+      <c r="BN19" s="120"/>
+      <c r="BO19" s="120"/>
+      <c r="BP19" s="120"/>
+      <c r="BQ19" s="120"/>
+      <c r="BR19" s="120"/>
+      <c r="BS19" s="120"/>
+      <c r="BT19" s="120"/>
+      <c r="BU19" s="120"/>
+      <c r="BV19" s="120"/>
+      <c r="BW19" s="120"/>
+      <c r="BX19" s="120"/>
+      <c r="BY19" s="120"/>
+      <c r="BZ19" s="120"/>
+      <c r="CA19" s="120"/>
+      <c r="CB19" s="120"/>
+      <c r="CC19" s="120"/>
+      <c r="CD19" s="120"/>
+      <c r="CE19" s="120"/>
+      <c r="CF19" s="120"/>
+      <c r="CG19" s="120"/>
+      <c r="CH19" s="120"/>
+      <c r="CI19" s="120"/>
+      <c r="CJ19" s="120"/>
+      <c r="CK19" s="120"/>
+      <c r="CL19" s="120"/>
+      <c r="CM19" s="120"/>
+      <c r="CN19" s="120"/>
+      <c r="CO19" s="120"/>
+      <c r="CP19" s="120"/>
+      <c r="CQ19" s="120"/>
+      <c r="CR19" s="120"/>
+      <c r="CS19" s="120"/>
+      <c r="CT19" s="120"/>
+      <c r="CU19" s="120"/>
+      <c r="CV19" s="120"/>
+    </row>
+    <row r="20" spans="1:100" ht="60" customHeight="1">
+      <c r="A20" s="60"/>
+      <c r="B20" s="122" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="123"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="125"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="123"/>
+      <c r="M20" s="124"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="123"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="124"/>
+      <c r="T20" s="125"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="124"/>
+      <c r="W20" s="125"/>
+      <c r="AW20" s="126" t="s">
+        <v>51</v>
+      </c>
+      <c r="AX20" s="126"/>
+      <c r="AY20" s="127"/>
+      <c r="AZ20" s="127"/>
+      <c r="BA20" s="127"/>
+      <c r="BB20" s="128"/>
+      <c r="BC20" s="127"/>
+      <c r="BD20" s="127"/>
+      <c r="BE20" s="127"/>
+      <c r="BF20" s="127"/>
+      <c r="BG20" s="127"/>
+      <c r="BH20" s="127"/>
+      <c r="BI20" s="127"/>
+      <c r="BJ20" s="127"/>
+      <c r="BK20" s="128"/>
+      <c r="BL20" s="127"/>
+      <c r="BM20" s="127"/>
+      <c r="BN20" s="127"/>
+      <c r="BO20" s="127"/>
+      <c r="BP20" s="127"/>
+      <c r="BQ20" s="127"/>
+      <c r="BR20" s="127"/>
+      <c r="BS20" s="127"/>
+      <c r="BT20" s="127"/>
+      <c r="BU20" s="127"/>
+      <c r="BV20" s="127"/>
+      <c r="BW20" s="127"/>
+      <c r="BX20" s="127"/>
+      <c r="BY20" s="127"/>
+      <c r="BZ20" s="127"/>
+      <c r="CA20" s="127"/>
+      <c r="CB20" s="127"/>
+      <c r="CC20" s="129"/>
+      <c r="CD20" s="127"/>
+      <c r="CE20" s="127"/>
+      <c r="CF20" s="127"/>
+      <c r="CG20" s="129"/>
+      <c r="CH20" s="129"/>
+      <c r="CI20" s="129"/>
+      <c r="CJ20" s="129"/>
+      <c r="CK20" s="129"/>
+      <c r="CL20" s="129"/>
+      <c r="CM20" s="129"/>
+      <c r="CN20" s="129"/>
+      <c r="CO20" s="129"/>
+      <c r="CP20" s="129"/>
+      <c r="CQ20" s="129"/>
+      <c r="CR20" s="129"/>
+      <c r="CS20" s="129"/>
+      <c r="CT20" s="129"/>
+      <c r="CU20" s="129"/>
+      <c r="CV20" s="129"/>
+    </row>
+    <row r="21" spans="1:100" ht="60" customHeight="1">
+      <c r="A21" s="60"/>
+      <c r="B21" s="122" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="130"/>
+      <c r="D21" s="131"/>
+      <c r="E21" s="132"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="130"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="132"/>
+      <c r="L21" s="130"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="132"/>
+      <c r="O21" s="130"/>
+      <c r="P21" s="131"/>
+      <c r="Q21" s="132"/>
+      <c r="R21" s="130"/>
+      <c r="S21" s="131"/>
+      <c r="T21" s="132"/>
+      <c r="U21" s="130"/>
+      <c r="V21" s="131"/>
+      <c r="W21" s="132"/>
+      <c r="AW21" s="133"/>
+      <c r="AX21" s="133"/>
+      <c r="AY21" s="134"/>
+      <c r="AZ21" s="134"/>
+      <c r="BA21" s="134"/>
+      <c r="BB21" s="134"/>
+      <c r="BC21" s="134"/>
+      <c r="BD21" s="134"/>
+      <c r="BE21" s="134"/>
+      <c r="BF21" s="134"/>
+      <c r="BG21" s="134"/>
+      <c r="BH21" s="134"/>
+      <c r="BI21" s="134"/>
+      <c r="BJ21" s="134"/>
+      <c r="BK21" s="135"/>
+      <c r="BL21" s="134"/>
+      <c r="BM21" s="134"/>
+      <c r="BN21" s="134"/>
+      <c r="BO21" s="134"/>
+      <c r="BP21" s="134"/>
+      <c r="BQ21" s="134"/>
+      <c r="BR21" s="134"/>
+      <c r="BS21" s="134"/>
+      <c r="BT21" s="134"/>
+      <c r="BU21" s="134"/>
+      <c r="BV21" s="134"/>
+      <c r="BW21" s="134"/>
+      <c r="BX21" s="134"/>
+      <c r="BY21" s="134"/>
+      <c r="BZ21" s="134"/>
+      <c r="CA21" s="134"/>
+      <c r="CB21" s="134"/>
+      <c r="CC21" s="134"/>
+      <c r="CD21" s="134"/>
+      <c r="CE21" s="134"/>
+      <c r="CF21" s="134"/>
+      <c r="CG21" s="134"/>
+      <c r="CH21" s="134"/>
+      <c r="CI21" s="134"/>
+      <c r="CJ21" s="134"/>
+      <c r="CK21" s="134"/>
+      <c r="CL21" s="134"/>
+      <c r="CM21" s="134"/>
+      <c r="CN21" s="134"/>
+      <c r="CO21" s="134"/>
+      <c r="CP21" s="134"/>
+      <c r="CQ21" s="134"/>
+      <c r="CR21" s="134"/>
+      <c r="CS21" s="134"/>
+      <c r="CT21" s="134"/>
+      <c r="CU21" s="134"/>
+      <c r="CV21" s="134"/>
+    </row>
+    <row r="22" spans="1:100" ht="60" customHeight="1">
+      <c r="A22" s="60"/>
+      <c r="B22" s="94" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="136"/>
+      <c r="G22" s="137"/>
+      <c r="H22" s="138"/>
+      <c r="I22" s="136"/>
+      <c r="J22" s="137"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="136"/>
+      <c r="M22" s="137"/>
+      <c r="N22" s="138"/>
+      <c r="O22" s="136"/>
+      <c r="P22" s="137"/>
+      <c r="Q22" s="138"/>
+      <c r="R22" s="136"/>
+      <c r="S22" s="137"/>
+      <c r="T22" s="138"/>
+      <c r="U22" s="136"/>
+      <c r="V22" s="137"/>
+      <c r="W22" s="138"/>
+      <c r="AW22" s="139" t="s">
+        <v>52</v>
+      </c>
+      <c r="AX22" s="139"/>
+      <c r="AY22" s="140">
+        <f>$X36*AY14</f>
+        <v>-420000</v>
+      </c>
+      <c r="AZ22" s="140">
+        <f>$X36*AZ14</f>
+        <v>-840000</v>
+      </c>
+      <c r="BA22" s="140">
+        <f>$X36*BA14</f>
+        <v>-1260000</v>
+      </c>
+      <c r="BB22" s="140">
+        <f t="shared" ref="BB22:CV22" si="52">$X36*BB14</f>
+        <v>-1680000</v>
+      </c>
+      <c r="BC22" s="140">
+        <f t="shared" si="52"/>
+        <v>-2100000</v>
+      </c>
+      <c r="BD22" s="140">
+        <f t="shared" si="52"/>
+        <v>-2520000</v>
+      </c>
+      <c r="BE22" s="140">
+        <f t="shared" si="52"/>
+        <v>-2940000</v>
+      </c>
+      <c r="BF22" s="140">
+        <f t="shared" si="52"/>
+        <v>-3360000</v>
+      </c>
+      <c r="BG22" s="140">
+        <f t="shared" si="52"/>
+        <v>-3780000</v>
+      </c>
+      <c r="BH22" s="140">
+        <f t="shared" si="52"/>
+        <v>-4200000</v>
+      </c>
+      <c r="BI22" s="140">
+        <f t="shared" si="52"/>
+        <v>-4620000</v>
+      </c>
+      <c r="BJ22" s="140">
+        <f t="shared" si="52"/>
+        <v>-5040000</v>
+      </c>
+      <c r="BK22" s="141">
+        <f t="shared" si="52"/>
+        <v>-5460000</v>
+      </c>
+      <c r="BL22" s="140">
+        <f t="shared" si="52"/>
+        <v>-5880000</v>
+      </c>
+      <c r="BM22" s="140">
+        <f t="shared" si="52"/>
+        <v>-6300000</v>
+      </c>
+      <c r="BN22" s="140">
+        <f t="shared" si="52"/>
+        <v>-6720000</v>
+      </c>
+      <c r="BO22" s="140">
+        <f t="shared" si="52"/>
+        <v>-7140000</v>
+      </c>
+      <c r="BP22" s="140">
+        <f t="shared" si="52"/>
+        <v>-7560000</v>
+      </c>
+      <c r="BQ22" s="140">
+        <f t="shared" si="52"/>
+        <v>-7980000</v>
+      </c>
+      <c r="BR22" s="140">
+        <f t="shared" si="52"/>
+        <v>-8400000</v>
+      </c>
+      <c r="BS22" s="140">
+        <f t="shared" si="52"/>
+        <v>-8820000</v>
+      </c>
+      <c r="BT22" s="140">
+        <f t="shared" si="52"/>
+        <v>-9240000</v>
+      </c>
+      <c r="BU22" s="140">
+        <f t="shared" si="52"/>
+        <v>-9660000</v>
+      </c>
+      <c r="BV22" s="140">
+        <f t="shared" si="52"/>
+        <v>-10080000</v>
+      </c>
+      <c r="BW22" s="140">
+        <f t="shared" si="52"/>
+        <v>-10500000</v>
+      </c>
+      <c r="BX22" s="140">
+        <f t="shared" si="52"/>
+        <v>-10920000</v>
+      </c>
+      <c r="BY22" s="140">
+        <f t="shared" si="52"/>
+        <v>-11340000</v>
+      </c>
+      <c r="BZ22" s="140">
+        <f t="shared" si="52"/>
+        <v>-11760000</v>
+      </c>
+      <c r="CA22" s="140">
+        <f t="shared" si="52"/>
+        <v>-12180000</v>
+      </c>
+      <c r="CB22" s="140">
+        <f t="shared" si="52"/>
+        <v>-12600000</v>
+      </c>
+      <c r="CC22" s="140">
+        <f t="shared" si="52"/>
+        <v>-13020000</v>
+      </c>
+      <c r="CD22" s="140">
+        <f t="shared" si="52"/>
+        <v>-13440000</v>
+      </c>
+      <c r="CE22" s="140">
+        <f t="shared" si="52"/>
+        <v>-13860000</v>
+      </c>
+      <c r="CF22" s="140">
+        <f t="shared" si="52"/>
+        <v>-14280000</v>
+      </c>
+      <c r="CG22" s="140">
+        <f t="shared" si="52"/>
+        <v>-14700000</v>
+      </c>
+      <c r="CH22" s="140">
+        <f t="shared" si="52"/>
+        <v>-15120000</v>
+      </c>
+      <c r="CI22" s="140">
+        <f t="shared" si="52"/>
+        <v>-15540000</v>
+      </c>
+      <c r="CJ22" s="140">
+        <f t="shared" si="52"/>
+        <v>-15960000</v>
+      </c>
+      <c r="CK22" s="140">
+        <f t="shared" si="52"/>
+        <v>-16380000</v>
+      </c>
+      <c r="CL22" s="140">
+        <f t="shared" si="52"/>
+        <v>-16800000</v>
+      </c>
+      <c r="CM22" s="140">
+        <f t="shared" si="52"/>
+        <v>-17220000</v>
+      </c>
+      <c r="CN22" s="140">
+        <f t="shared" si="52"/>
+        <v>-17640000</v>
+      </c>
+      <c r="CO22" s="140">
+        <f t="shared" si="52"/>
+        <v>-18060000</v>
+      </c>
+      <c r="CP22" s="140">
+        <f t="shared" si="52"/>
+        <v>-18480000</v>
+      </c>
+      <c r="CQ22" s="140">
+        <f t="shared" si="52"/>
+        <v>-18900000</v>
+      </c>
+      <c r="CR22" s="140">
+        <f t="shared" si="52"/>
+        <v>-19320000</v>
+      </c>
+      <c r="CS22" s="140">
+        <f t="shared" si="52"/>
+        <v>-19740000</v>
+      </c>
+      <c r="CT22" s="140">
+        <f t="shared" si="52"/>
+        <v>-20160000</v>
+      </c>
+      <c r="CU22" s="140">
+        <f t="shared" si="52"/>
+        <v>-20580000</v>
+      </c>
+      <c r="CV22" s="140">
+        <f t="shared" si="52"/>
+        <v>-21000000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:100" ht="20.25" customHeight="1">
+      <c r="A23" s="60"/>
+      <c r="B23" s="142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="143"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="145" t="str">
+        <f>IFERROR(IF(C25=0,"",DATEDIF($C$7,C25,"ｍ")),"")</f>
         <v/>
       </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="73" t="str">
-        <f>IF(F9&lt;&gt;"", DATE(YEAR($B$1), MONTH($B$1)+3, 1), "")</f>
+      <c r="F23" s="143"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="145" t="str">
+        <f>IFERROR(IF(F25=0,"",DATEDIF($C$7,F25,"ｍ")),"")</f>
         <v/>
       </c>
-      <c r="G10" s="74"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="73" t="str">
-        <f>IF(I9&lt;&gt;"", DATE(YEAR($B$1), MONTH($B$1)+3, 1), "")</f>
+      <c r="I23" s="143"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="145" t="str">
+        <f>IFERROR(IF(I25=0,"",DATEDIF($C$7,I25,"ｍ")),"")</f>
         <v/>
       </c>
-      <c r="J10" s="74"/>
-      <c r="K10" s="75"/>
-      <c r="L10" s="73" t="str">
-        <f>IF(L9&lt;&gt;"", DATE(YEAR($B$1), MONTH($B$1)+3, 1), "")</f>
+      <c r="L23" s="143"/>
+      <c r="M23" s="144"/>
+      <c r="N23" s="145" t="str">
+        <f>IFERROR(IF(L25=0,"",DATEDIF($C$7,L25,"ｍ")),"")</f>
         <v/>
       </c>
-      <c r="M10" s="74"/>
-      <c r="N10" s="75"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="144"/>
+      <c r="Q23" s="145" t="str">
+        <f>IFERROR(IF(O25=0,"",DATEDIF($C$7,O25,"ｍ")),"")</f>
+        <v/>
+      </c>
+      <c r="R23" s="143"/>
+      <c r="S23" s="144"/>
+      <c r="T23" s="145" t="str">
+        <f>IFERROR(IF(R25=0,"",DATEDIF($C$7,R25,"ｍ")),"")</f>
+        <v/>
+      </c>
+      <c r="U23" s="143"/>
+      <c r="V23" s="144"/>
+      <c r="W23" s="145" t="str">
+        <f>IFERROR(IF(U25=0,"",DATEDIF($C$7,U25,"ｍ")),"")</f>
+        <v/>
+      </c>
+      <c r="X23" s="146"/>
+      <c r="Y23" s="147"/>
+      <c r="Z23" s="147"/>
+      <c r="AW23" s="148"/>
+      <c r="AX23" s="148"/>
+      <c r="AY23" s="148"/>
+      <c r="AZ23" s="148"/>
+      <c r="BA23" s="148"/>
+      <c r="BB23" s="148"/>
+      <c r="BC23" s="148"/>
+      <c r="BD23" s="148"/>
+      <c r="BE23" s="148"/>
+      <c r="BF23" s="148"/>
+      <c r="BG23" s="148"/>
+      <c r="BH23" s="148"/>
+      <c r="BI23" s="148"/>
+      <c r="BJ23" s="148"/>
+      <c r="BK23" s="148"/>
+      <c r="BL23" s="148"/>
+      <c r="BM23" s="148"/>
+      <c r="BN23" s="148"/>
+      <c r="BO23" s="148"/>
+      <c r="BP23" s="149"/>
+      <c r="BQ23" s="148"/>
+      <c r="BR23" s="148"/>
+      <c r="BS23" s="148"/>
+      <c r="BT23" s="148"/>
+      <c r="BU23" s="148"/>
+      <c r="BV23" s="148"/>
+      <c r="BW23" s="148"/>
+      <c r="BX23" s="148"/>
+      <c r="BY23" s="148"/>
+      <c r="BZ23" s="148"/>
+      <c r="CA23" s="148"/>
+      <c r="CB23" s="148"/>
+      <c r="CC23" s="148"/>
+      <c r="CD23" s="148"/>
+      <c r="CE23" s="148"/>
+      <c r="CF23" s="148"/>
+      <c r="CG23" s="148"/>
+      <c r="CH23" s="148"/>
+      <c r="CI23" s="148"/>
+      <c r="CJ23" s="148"/>
+      <c r="CK23" s="148"/>
+      <c r="CL23" s="148"/>
+      <c r="CM23" s="148"/>
+      <c r="CN23" s="148"/>
+      <c r="CO23" s="148"/>
+      <c r="CP23" s="148"/>
+      <c r="CQ23" s="148"/>
+      <c r="CR23" s="148"/>
+      <c r="CS23" s="148"/>
+      <c r="CT23" s="148"/>
+      <c r="CU23" s="148"/>
+      <c r="CV23" s="148"/>
     </row>
-    <row r="11" spans="1:14" ht="58" customHeight="1">
-      <c r="A11" s="94"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="76"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="78"/>
-      <c r="F11" s="76"/>
-      <c r="G11" s="77"/>
-      <c r="H11" s="78"/>
-      <c r="I11" s="76"/>
-      <c r="J11" s="77"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="77"/>
-      <c r="N11" s="78"/>
+    <row r="24" spans="1:100" ht="18.75" customHeight="1">
+      <c r="A24" s="60"/>
+      <c r="B24" s="150"/>
+      <c r="C24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="152"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="152"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="J24" s="152"/>
+      <c r="K24" s="153"/>
+      <c r="L24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="M24" s="152"/>
+      <c r="N24" s="153"/>
+      <c r="O24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="P24" s="152"/>
+      <c r="Q24" s="153"/>
+      <c r="R24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="S24" s="152"/>
+      <c r="T24" s="153"/>
+      <c r="U24" s="151" t="s">
+        <v>12</v>
+      </c>
+      <c r="V24" s="152"/>
+      <c r="W24" s="153"/>
+      <c r="X24" s="146"/>
+      <c r="Y24" s="147"/>
+      <c r="Z24" s="147"/>
+      <c r="AM24" s="154"/>
+      <c r="AN24" s="154"/>
+      <c r="AO24" s="154"/>
+      <c r="AP24" s="154"/>
+      <c r="AQ24" s="154"/>
+      <c r="AR24" s="154"/>
+      <c r="AS24" s="154"/>
+      <c r="AT24" s="154"/>
+      <c r="AU24" s="154"/>
+      <c r="AV24" s="154"/>
+      <c r="AW24" s="155"/>
+      <c r="AX24" s="155"/>
+      <c r="AY24" s="155"/>
+      <c r="AZ24" s="155"/>
+      <c r="BA24" s="155"/>
+      <c r="BB24" s="155"/>
+      <c r="BC24" s="155"/>
+      <c r="BD24" s="155"/>
+      <c r="BE24" s="155"/>
+      <c r="BF24" s="155"/>
+      <c r="BG24" s="155"/>
+      <c r="BH24" s="155"/>
+      <c r="BI24" s="156"/>
+      <c r="BJ24" s="156"/>
+      <c r="BK24" s="156"/>
+      <c r="BL24" s="156"/>
+      <c r="BM24" s="156"/>
+      <c r="BN24" s="156"/>
+      <c r="BO24" s="156"/>
+      <c r="BP24" s="156"/>
+      <c r="BQ24" s="156"/>
+      <c r="BR24" s="156"/>
+      <c r="BS24" s="156"/>
+      <c r="BT24" s="156"/>
+      <c r="BU24" s="156"/>
+      <c r="BV24" s="156"/>
+      <c r="BW24" s="156"/>
+      <c r="BX24" s="156"/>
+      <c r="BY24" s="156"/>
+      <c r="BZ24" s="156"/>
+      <c r="CA24" s="156"/>
+      <c r="CB24" s="156"/>
+      <c r="CC24" s="156"/>
+      <c r="CD24" s="156"/>
+      <c r="CE24" s="156"/>
+      <c r="CF24" s="156"/>
+      <c r="CG24" s="156"/>
+      <c r="CH24" s="156"/>
+      <c r="CI24" s="156"/>
+      <c r="CJ24" s="156"/>
+      <c r="CK24" s="156"/>
+      <c r="CL24" s="156"/>
+      <c r="CM24" s="156"/>
+      <c r="CN24" s="156"/>
+      <c r="CO24" s="156"/>
+      <c r="CP24" s="156"/>
+      <c r="CQ24" s="156"/>
+      <c r="CR24" s="156"/>
+      <c r="CS24" s="156"/>
+      <c r="CT24" s="156"/>
+      <c r="CU24" s="156"/>
+      <c r="CV24" s="156"/>
     </row>
-    <row r="12" spans="1:14" ht="58" customHeight="1">
-      <c r="A12" s="94"/>
-      <c r="B12" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="79"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="79"/>
-      <c r="J12" s="80"/>
-      <c r="K12" s="81"/>
-      <c r="L12" s="79"/>
-      <c r="M12" s="80"/>
-      <c r="N12" s="81"/>
+    <row r="25" spans="1:100" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A25" s="70"/>
+      <c r="B25" s="157"/>
+      <c r="C25" s="158"/>
+      <c r="D25" s="159"/>
+      <c r="E25" s="160" t="str">
+        <f>IF(C23=0,"",DATEDIF(C23,C25,"y"))</f>
+        <v/>
+      </c>
+      <c r="F25" s="158"/>
+      <c r="G25" s="159"/>
+      <c r="H25" s="160" t="str">
+        <f>IF(F23=0,"",DATEDIF(F23,F25,"y"))</f>
+        <v/>
+      </c>
+      <c r="I25" s="158"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="160" t="str">
+        <f>IF(I23=0,"",DATEDIF(I23,I25,"y"))</f>
+        <v/>
+      </c>
+      <c r="L25" s="158"/>
+      <c r="M25" s="159"/>
+      <c r="N25" s="160" t="str">
+        <f>IF(L23=0,"",DATEDIF(L23,L25,"y"))</f>
+        <v/>
+      </c>
+      <c r="O25" s="158"/>
+      <c r="P25" s="159"/>
+      <c r="Q25" s="160" t="str">
+        <f>IF(O23=0,"",DATEDIF(O23,O25,"y"))</f>
+        <v/>
+      </c>
+      <c r="R25" s="158"/>
+      <c r="S25" s="159"/>
+      <c r="T25" s="160" t="str">
+        <f>IF(R23=0,"",DATEDIF(R23,R25,"y"))</f>
+        <v/>
+      </c>
+      <c r="U25" s="158"/>
+      <c r="V25" s="159"/>
+      <c r="W25" s="160" t="str">
+        <f>IF(U23=0,"",DATEDIF(U23,U25,"y"))</f>
+        <v/>
+      </c>
+      <c r="X25" s="161"/>
+      <c r="Y25" s="162"/>
+      <c r="Z25" s="162"/>
+      <c r="AM25" s="154"/>
+      <c r="AN25" s="154"/>
+      <c r="AO25" s="154"/>
+      <c r="AP25" s="154"/>
+      <c r="AQ25" s="154"/>
+      <c r="AR25" s="154"/>
+      <c r="AS25" s="154"/>
+      <c r="AT25" s="154"/>
+      <c r="AU25" s="154"/>
+      <c r="AV25" s="154"/>
+      <c r="AW25" s="133"/>
+      <c r="AX25" s="133"/>
+      <c r="AY25" s="133"/>
+      <c r="AZ25" s="133"/>
+      <c r="BA25" s="133"/>
+      <c r="BB25" s="133"/>
+      <c r="BC25" s="133"/>
+      <c r="BD25" s="133"/>
+      <c r="BE25" s="133"/>
+      <c r="BF25" s="133"/>
+      <c r="BG25" s="133"/>
+      <c r="BH25" s="133"/>
+      <c r="BI25" s="163"/>
+      <c r="BJ25" s="163"/>
+      <c r="BK25" s="163"/>
+      <c r="BL25" s="163"/>
+      <c r="BM25" s="163"/>
+      <c r="BN25" s="163"/>
+      <c r="BO25" s="163"/>
+      <c r="BP25" s="163"/>
+      <c r="BQ25" s="163"/>
+      <c r="BR25" s="163"/>
+      <c r="BS25" s="163"/>
+      <c r="BT25" s="163"/>
+      <c r="BU25" s="163"/>
+      <c r="BV25" s="163"/>
+      <c r="BW25" s="163"/>
+      <c r="BX25" s="163"/>
+      <c r="BY25" s="163"/>
+      <c r="BZ25" s="163"/>
+      <c r="CA25" s="163"/>
+      <c r="CB25" s="163"/>
+      <c r="CC25" s="163"/>
+      <c r="CD25" s="163"/>
+      <c r="CE25" s="163"/>
+      <c r="CF25" s="163"/>
+      <c r="CG25" s="163"/>
+      <c r="CH25" s="163"/>
+      <c r="CI25" s="163"/>
+      <c r="CJ25" s="163"/>
+      <c r="CK25" s="163"/>
+      <c r="CL25" s="163"/>
+      <c r="CM25" s="163"/>
+      <c r="CN25" s="163"/>
+      <c r="CO25" s="163"/>
+      <c r="CP25" s="163"/>
+      <c r="CQ25" s="163"/>
+      <c r="CR25" s="163"/>
+      <c r="CS25" s="163"/>
+      <c r="CT25" s="163"/>
+      <c r="CU25" s="163"/>
+      <c r="CV25" s="163"/>
     </row>
-    <row r="13" spans="1:14" ht="58" customHeight="1">
-      <c r="A13" s="94"/>
-      <c r="B13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="82"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="82"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="82"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="82"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="84"/>
+    <row r="26" spans="1:100" ht="60" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A26" s="164" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="165" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="167"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="167"/>
+      <c r="H26" s="168"/>
+      <c r="I26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="J26" s="167"/>
+      <c r="K26" s="168"/>
+      <c r="L26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="M26" s="167"/>
+      <c r="N26" s="168"/>
+      <c r="O26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="P26" s="167"/>
+      <c r="Q26" s="168"/>
+      <c r="R26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="S26" s="167"/>
+      <c r="T26" s="168"/>
+      <c r="U26" s="166" t="s">
+        <v>68</v>
+      </c>
+      <c r="V26" s="167"/>
+      <c r="W26" s="168"/>
+      <c r="X26" s="169">
+        <f>SUM(D26,G26,J26,M26,P26,S26,V26)</f>
+        <v>0</v>
+      </c>
+      <c r="Y26" s="170"/>
+      <c r="Z26" s="171"/>
+      <c r="AM26" s="154"/>
+      <c r="AN26" s="154"/>
+      <c r="AO26" s="154"/>
+      <c r="AP26" s="154"/>
+      <c r="AQ26" s="154"/>
+      <c r="AR26" s="154"/>
+      <c r="AS26" s="154"/>
+      <c r="AT26" s="154"/>
+      <c r="AU26" s="154"/>
+      <c r="AV26" s="154"/>
+      <c r="AW26" s="133"/>
+      <c r="AX26" s="133"/>
+      <c r="AY26" s="133"/>
+      <c r="AZ26" s="133"/>
+      <c r="BA26" s="133"/>
+      <c r="BB26" s="133"/>
+      <c r="BC26" s="133"/>
+      <c r="BD26" s="133"/>
+      <c r="BE26" s="133"/>
+      <c r="BF26" s="133"/>
+      <c r="BG26" s="133"/>
+      <c r="BH26" s="133"/>
+      <c r="BI26" s="163"/>
+      <c r="BJ26" s="163"/>
+      <c r="BK26" s="163"/>
+      <c r="BL26" s="163"/>
+      <c r="BM26" s="163"/>
+      <c r="BN26" s="163"/>
+      <c r="BO26" s="163"/>
+      <c r="BP26" s="163"/>
+      <c r="BQ26" s="163"/>
+      <c r="BR26" s="163"/>
+      <c r="BS26" s="163"/>
+      <c r="BT26" s="163"/>
+      <c r="BU26" s="163"/>
+      <c r="BV26" s="163"/>
+      <c r="BW26" s="163"/>
+      <c r="BX26" s="163"/>
+      <c r="BY26" s="163"/>
+      <c r="BZ26" s="163"/>
+      <c r="CA26" s="163"/>
+      <c r="CB26" s="163"/>
+      <c r="CC26" s="163"/>
+      <c r="CD26" s="163"/>
+      <c r="CE26" s="163"/>
+      <c r="CF26" s="163"/>
+      <c r="CG26" s="163"/>
+      <c r="CH26" s="163"/>
+      <c r="CI26" s="163"/>
+      <c r="CJ26" s="163"/>
+      <c r="CK26" s="163"/>
+      <c r="CL26" s="163"/>
+      <c r="CM26" s="163"/>
+      <c r="CN26" s="163"/>
+      <c r="CO26" s="163"/>
+      <c r="CP26" s="163"/>
+      <c r="CQ26" s="163"/>
+      <c r="CR26" s="163"/>
+      <c r="CS26" s="163"/>
+      <c r="CT26" s="163"/>
+      <c r="CU26" s="163"/>
+      <c r="CV26" s="163"/>
     </row>
-    <row r="14" spans="1:14" ht="58" customHeight="1">
-      <c r="A14" s="94"/>
-      <c r="B14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="87"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="87"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="86"/>
-      <c r="N14" s="87"/>
+    <row r="27" spans="1:100" ht="18.75" customHeight="1" thickTop="1">
+      <c r="A27" s="172"/>
+      <c r="B27" s="173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="174"/>
+      <c r="D27" s="175"/>
+      <c r="E27" s="176"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="176"/>
+      <c r="I27" s="174"/>
+      <c r="J27" s="175"/>
+      <c r="K27" s="176"/>
+      <c r="L27" s="174"/>
+      <c r="M27" s="175"/>
+      <c r="N27" s="176"/>
+      <c r="O27" s="174"/>
+      <c r="P27" s="175"/>
+      <c r="Q27" s="176"/>
+      <c r="R27" s="174"/>
+      <c r="S27" s="175"/>
+      <c r="T27" s="176"/>
+      <c r="U27" s="174"/>
+      <c r="V27" s="175"/>
+      <c r="W27" s="176"/>
+      <c r="AM27" s="154"/>
+      <c r="AN27" s="154"/>
+      <c r="AO27" s="154"/>
+      <c r="AP27" s="154"/>
+      <c r="AQ27" s="154"/>
+      <c r="AR27" s="154"/>
+      <c r="AS27" s="154"/>
+      <c r="AT27" s="154"/>
+      <c r="AU27" s="154"/>
+      <c r="AV27" s="154"/>
+      <c r="AW27" s="133"/>
+      <c r="AX27" s="133"/>
+      <c r="AY27" s="133"/>
+      <c r="AZ27" s="133"/>
+      <c r="BA27" s="133"/>
+      <c r="BB27" s="133"/>
+      <c r="BC27" s="133"/>
+      <c r="BD27" s="133"/>
+      <c r="BE27" s="133"/>
+      <c r="BF27" s="133"/>
+      <c r="BG27" s="133"/>
+      <c r="BH27" s="133"/>
+      <c r="BI27" s="163"/>
+      <c r="BJ27" s="163"/>
+      <c r="BK27" s="163"/>
+      <c r="BL27" s="163"/>
+      <c r="BM27" s="163"/>
+      <c r="BN27" s="163"/>
+      <c r="BO27" s="163"/>
+      <c r="BP27" s="163"/>
+      <c r="BQ27" s="163"/>
+      <c r="BR27" s="163"/>
+      <c r="BS27" s="163"/>
+      <c r="BT27" s="163"/>
+      <c r="BU27" s="163"/>
+      <c r="BV27" s="163"/>
+      <c r="BW27" s="163"/>
+      <c r="BX27" s="163"/>
+      <c r="BY27" s="163"/>
+      <c r="BZ27" s="163"/>
+      <c r="CA27" s="163"/>
+      <c r="CB27" s="163"/>
+      <c r="CC27" s="163"/>
+      <c r="CD27" s="163"/>
+      <c r="CE27" s="163"/>
+      <c r="CF27" s="163"/>
+      <c r="CG27" s="163"/>
+      <c r="CH27" s="163"/>
+      <c r="CI27" s="163"/>
+      <c r="CJ27" s="163"/>
+      <c r="CK27" s="163"/>
+      <c r="CL27" s="163"/>
+      <c r="CM27" s="163"/>
+      <c r="CN27" s="163"/>
+      <c r="CO27" s="163"/>
+      <c r="CP27" s="163"/>
+      <c r="CQ27" s="163"/>
+      <c r="CR27" s="163"/>
+      <c r="CS27" s="163"/>
+      <c r="CT27" s="163"/>
+      <c r="CU27" s="163"/>
+      <c r="CV27" s="163"/>
     </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="94"/>
-      <c r="B15" s="98" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="89"/>
-      <c r="E15" s="90" t="str">
-        <f ca="1">IFERROR(IF(C17=0,"",DATEDIF($B$1,C17,"ｍ")),"")</f>
+    <row r="28" spans="1:100" ht="18.75" customHeight="1">
+      <c r="A28" s="172"/>
+      <c r="B28" s="177"/>
+      <c r="C28" s="178"/>
+      <c r="D28" s="179"/>
+      <c r="E28" s="180"/>
+      <c r="F28" s="178"/>
+      <c r="G28" s="179"/>
+      <c r="H28" s="180"/>
+      <c r="I28" s="178"/>
+      <c r="J28" s="179"/>
+      <c r="K28" s="180"/>
+      <c r="L28" s="178"/>
+      <c r="M28" s="179"/>
+      <c r="N28" s="180"/>
+      <c r="O28" s="178"/>
+      <c r="P28" s="179"/>
+      <c r="Q28" s="180"/>
+      <c r="R28" s="178"/>
+      <c r="S28" s="179"/>
+      <c r="T28" s="180"/>
+      <c r="U28" s="178"/>
+      <c r="V28" s="179"/>
+      <c r="W28" s="180"/>
+      <c r="AM28" s="154"/>
+      <c r="AN28" s="154"/>
+      <c r="AO28" s="154"/>
+      <c r="AP28" s="154"/>
+      <c r="AQ28" s="154"/>
+      <c r="AR28" s="154"/>
+      <c r="AS28" s="154"/>
+      <c r="AT28" s="154"/>
+      <c r="AU28" s="154"/>
+      <c r="AV28" s="154"/>
+      <c r="AW28" s="133"/>
+      <c r="AX28" s="133"/>
+      <c r="AY28" s="133"/>
+      <c r="AZ28" s="133"/>
+      <c r="BA28" s="133"/>
+      <c r="BB28" s="133"/>
+      <c r="BC28" s="133"/>
+      <c r="BD28" s="133"/>
+      <c r="BE28" s="133"/>
+      <c r="BF28" s="133"/>
+      <c r="BG28" s="133"/>
+      <c r="BH28" s="133"/>
+      <c r="BI28" s="163"/>
+      <c r="BJ28" s="163"/>
+      <c r="BK28" s="163"/>
+      <c r="BL28" s="163"/>
+      <c r="BM28" s="163"/>
+      <c r="BN28" s="163"/>
+      <c r="BO28" s="163"/>
+      <c r="BP28" s="163"/>
+      <c r="BQ28" s="163"/>
+      <c r="BR28" s="163"/>
+      <c r="BS28" s="163"/>
+      <c r="BT28" s="163"/>
+      <c r="BU28" s="163"/>
+      <c r="BV28" s="163"/>
+      <c r="BW28" s="163"/>
+      <c r="BX28" s="163"/>
+      <c r="BY28" s="163"/>
+      <c r="BZ28" s="163"/>
+      <c r="CA28" s="163"/>
+      <c r="CB28" s="163"/>
+      <c r="CC28" s="163"/>
+      <c r="CD28" s="163"/>
+      <c r="CE28" s="163"/>
+      <c r="CF28" s="163"/>
+      <c r="CG28" s="163"/>
+      <c r="CH28" s="163"/>
+      <c r="CI28" s="163"/>
+      <c r="CJ28" s="163"/>
+      <c r="CK28" s="163"/>
+      <c r="CL28" s="163"/>
+      <c r="CM28" s="163"/>
+      <c r="CN28" s="163"/>
+      <c r="CO28" s="163"/>
+      <c r="CP28" s="163"/>
+      <c r="CQ28" s="163"/>
+      <c r="CR28" s="163"/>
+      <c r="CS28" s="163"/>
+      <c r="CT28" s="163"/>
+      <c r="CU28" s="163"/>
+      <c r="CV28" s="163"/>
+    </row>
+    <row r="29" spans="1:100" ht="18.75" customHeight="1" thickBot="1">
+      <c r="A29" s="172"/>
+      <c r="B29" s="181"/>
+      <c r="C29" s="182"/>
+      <c r="D29" s="183"/>
+      <c r="E29" s="184"/>
+      <c r="F29" s="182"/>
+      <c r="G29" s="183"/>
+      <c r="H29" s="184"/>
+      <c r="I29" s="182"/>
+      <c r="J29" s="183"/>
+      <c r="K29" s="184"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="183"/>
+      <c r="N29" s="184"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
+      <c r="R29" s="182"/>
+      <c r="S29" s="183"/>
+      <c r="T29" s="184"/>
+      <c r="U29" s="182"/>
+      <c r="V29" s="183"/>
+      <c r="W29" s="184"/>
+      <c r="AM29" s="154"/>
+      <c r="AN29" s="154"/>
+      <c r="AO29" s="154"/>
+      <c r="AP29" s="154"/>
+      <c r="AQ29" s="154"/>
+      <c r="AR29" s="154"/>
+      <c r="AS29" s="154"/>
+      <c r="AT29" s="154"/>
+      <c r="AU29" s="154"/>
+      <c r="AV29" s="154"/>
+      <c r="AW29" s="133"/>
+      <c r="AX29" s="133"/>
+      <c r="AY29" s="133"/>
+      <c r="AZ29" s="133"/>
+      <c r="BA29" s="133"/>
+      <c r="BB29" s="133"/>
+      <c r="BC29" s="133"/>
+      <c r="BD29" s="133"/>
+      <c r="BE29" s="133"/>
+      <c r="BF29" s="133"/>
+      <c r="BG29" s="133"/>
+      <c r="BH29" s="133"/>
+      <c r="BI29" s="163"/>
+      <c r="BJ29" s="163"/>
+      <c r="BK29" s="163"/>
+      <c r="BL29" s="163"/>
+      <c r="BM29" s="163"/>
+      <c r="BN29" s="163"/>
+      <c r="BO29" s="163"/>
+      <c r="BP29" s="163"/>
+      <c r="BQ29" s="163"/>
+      <c r="BR29" s="163"/>
+      <c r="BS29" s="163"/>
+      <c r="BT29" s="163"/>
+      <c r="BU29" s="163"/>
+      <c r="BV29" s="163"/>
+      <c r="BW29" s="163"/>
+      <c r="BX29" s="163"/>
+      <c r="BY29" s="163"/>
+      <c r="BZ29" s="163"/>
+      <c r="CA29" s="163"/>
+      <c r="CB29" s="163"/>
+      <c r="CC29" s="163"/>
+      <c r="CD29" s="163"/>
+      <c r="CE29" s="163"/>
+      <c r="CF29" s="163"/>
+      <c r="CG29" s="163"/>
+      <c r="CH29" s="163"/>
+      <c r="CI29" s="163"/>
+      <c r="CJ29" s="163"/>
+      <c r="CK29" s="163"/>
+      <c r="CL29" s="163"/>
+      <c r="CM29" s="163"/>
+      <c r="CN29" s="163"/>
+      <c r="CO29" s="163"/>
+      <c r="CP29" s="163"/>
+      <c r="CQ29" s="163"/>
+      <c r="CR29" s="163"/>
+      <c r="CS29" s="163"/>
+      <c r="CT29" s="163"/>
+      <c r="CU29" s="163"/>
+      <c r="CV29" s="163"/>
+    </row>
+    <row r="30" spans="1:100" ht="60" customHeight="1">
+      <c r="A30" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="185" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="186"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="188"/>
+      <c r="F30" s="186"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="188"/>
+      <c r="I30" s="186"/>
+      <c r="J30" s="187"/>
+      <c r="K30" s="188"/>
+      <c r="L30" s="186"/>
+      <c r="M30" s="187"/>
+      <c r="N30" s="188"/>
+      <c r="O30" s="186"/>
+      <c r="P30" s="187"/>
+      <c r="Q30" s="188"/>
+      <c r="R30" s="186"/>
+      <c r="S30" s="187"/>
+      <c r="T30" s="188"/>
+      <c r="U30" s="186"/>
+      <c r="V30" s="187"/>
+      <c r="W30" s="188"/>
+      <c r="X30" s="189">
+        <f>C30+F30+I30+L30+C31+F31+I31+L31+O30+O31+U30+U31+R30+R31</f>
+        <v>0</v>
+      </c>
+      <c r="Y30" s="190"/>
+      <c r="Z30" s="191"/>
+      <c r="AM30" s="154"/>
+      <c r="AN30" s="154"/>
+      <c r="AO30" s="154"/>
+      <c r="AP30" s="154"/>
+      <c r="AQ30" s="154"/>
+      <c r="AR30" s="154"/>
+      <c r="AS30" s="154"/>
+      <c r="AT30" s="154"/>
+      <c r="AU30" s="154"/>
+      <c r="AV30" s="154"/>
+      <c r="AW30" s="133"/>
+      <c r="AX30" s="133"/>
+      <c r="AY30" s="133"/>
+      <c r="AZ30" s="133"/>
+      <c r="BA30" s="133"/>
+      <c r="BB30" s="133"/>
+      <c r="BC30" s="133"/>
+      <c r="BD30" s="133"/>
+      <c r="BE30" s="133"/>
+      <c r="BF30" s="133"/>
+      <c r="BG30" s="133"/>
+      <c r="BH30" s="133"/>
+      <c r="BI30" s="163"/>
+      <c r="BJ30" s="163"/>
+      <c r="BK30" s="163"/>
+      <c r="BL30" s="163"/>
+      <c r="BM30" s="163"/>
+      <c r="BN30" s="163"/>
+      <c r="BO30" s="163"/>
+      <c r="BP30" s="163"/>
+      <c r="BQ30" s="163"/>
+      <c r="BR30" s="163"/>
+      <c r="BS30" s="163"/>
+      <c r="BT30" s="163"/>
+      <c r="BU30" s="163"/>
+      <c r="BV30" s="163"/>
+      <c r="BW30" s="163"/>
+      <c r="BX30" s="163"/>
+      <c r="BY30" s="163"/>
+      <c r="BZ30" s="163"/>
+      <c r="CA30" s="163"/>
+      <c r="CB30" s="163"/>
+      <c r="CC30" s="163"/>
+      <c r="CD30" s="163"/>
+      <c r="CE30" s="163"/>
+      <c r="CF30" s="163"/>
+      <c r="CG30" s="163"/>
+      <c r="CH30" s="163"/>
+      <c r="CI30" s="163"/>
+      <c r="CJ30" s="163"/>
+      <c r="CK30" s="163"/>
+      <c r="CL30" s="163"/>
+      <c r="CM30" s="163"/>
+      <c r="CN30" s="163"/>
+      <c r="CO30" s="163"/>
+      <c r="CP30" s="163"/>
+      <c r="CQ30" s="163"/>
+      <c r="CR30" s="163"/>
+      <c r="CS30" s="163"/>
+      <c r="CT30" s="163"/>
+      <c r="CU30" s="163"/>
+      <c r="CV30" s="163"/>
+    </row>
+    <row r="31" spans="1:100" ht="60" customHeight="1" thickBot="1">
+      <c r="A31" s="60"/>
+      <c r="B31" s="192" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="186"/>
+      <c r="D31" s="187"/>
+      <c r="E31" s="188"/>
+      <c r="F31" s="186"/>
+      <c r="G31" s="187"/>
+      <c r="H31" s="188"/>
+      <c r="I31" s="186"/>
+      <c r="J31" s="187"/>
+      <c r="K31" s="188"/>
+      <c r="L31" s="186"/>
+      <c r="M31" s="187"/>
+      <c r="N31" s="188"/>
+      <c r="O31" s="186"/>
+      <c r="P31" s="187"/>
+      <c r="Q31" s="188"/>
+      <c r="R31" s="186"/>
+      <c r="S31" s="187"/>
+      <c r="T31" s="188"/>
+      <c r="U31" s="186"/>
+      <c r="V31" s="187"/>
+      <c r="W31" s="188"/>
+      <c r="X31" s="193"/>
+      <c r="Y31" s="194"/>
+      <c r="Z31" s="195"/>
+      <c r="AM31" s="154"/>
+      <c r="AN31" s="154"/>
+      <c r="AO31" s="154"/>
+      <c r="AP31" s="154"/>
+      <c r="AQ31" s="154"/>
+      <c r="AR31" s="154"/>
+      <c r="AS31" s="154"/>
+      <c r="AT31" s="154"/>
+      <c r="AU31" s="154"/>
+      <c r="AV31" s="154"/>
+      <c r="AW31" s="133"/>
+      <c r="AX31" s="133"/>
+      <c r="AY31" s="133"/>
+      <c r="AZ31" s="133"/>
+      <c r="BA31" s="133"/>
+      <c r="BB31" s="133"/>
+      <c r="BC31" s="133"/>
+      <c r="BD31" s="133"/>
+      <c r="BE31" s="133"/>
+      <c r="BF31" s="133"/>
+      <c r="BG31" s="133"/>
+      <c r="BH31" s="133"/>
+      <c r="BI31" s="163"/>
+      <c r="BJ31" s="163"/>
+      <c r="BK31" s="163"/>
+      <c r="BL31" s="163"/>
+      <c r="BM31" s="163"/>
+      <c r="BN31" s="163"/>
+      <c r="BO31" s="163"/>
+      <c r="BP31" s="163"/>
+      <c r="BQ31" s="163"/>
+      <c r="BR31" s="163"/>
+      <c r="BS31" s="163"/>
+      <c r="BT31" s="163"/>
+      <c r="BU31" s="163"/>
+      <c r="BV31" s="163"/>
+      <c r="BW31" s="163"/>
+      <c r="BX31" s="163"/>
+      <c r="BY31" s="163"/>
+      <c r="BZ31" s="163"/>
+      <c r="CA31" s="163"/>
+      <c r="CB31" s="163"/>
+      <c r="CC31" s="163"/>
+      <c r="CD31" s="163"/>
+      <c r="CE31" s="163"/>
+      <c r="CF31" s="163"/>
+      <c r="CG31" s="163"/>
+      <c r="CH31" s="163"/>
+      <c r="CI31" s="163"/>
+      <c r="CJ31" s="163"/>
+      <c r="CK31" s="163"/>
+      <c r="CL31" s="163"/>
+      <c r="CM31" s="163"/>
+      <c r="CN31" s="163"/>
+      <c r="CO31" s="163"/>
+      <c r="CP31" s="163"/>
+      <c r="CQ31" s="163"/>
+      <c r="CR31" s="163"/>
+      <c r="CS31" s="163"/>
+      <c r="CT31" s="163"/>
+      <c r="CU31" s="163"/>
+      <c r="CV31" s="163"/>
+    </row>
+    <row r="32" spans="1:100" ht="60" customHeight="1" thickBot="1">
+      <c r="A32" s="60"/>
+      <c r="B32" s="196" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" s="197"/>
+      <c r="D32" s="198"/>
+      <c r="E32" s="199"/>
+      <c r="F32" s="197" t="str">
+        <f>IF(F9="","",1100)</f>
         <v/>
       </c>
-      <c r="F15" s="88"/>
-      <c r="G15" s="89"/>
-      <c r="H15" s="90" t="str">
-        <f ca="1">IFERROR(IF(F17=0,"",DATEDIF($B$1,F17,"ｍ")),"")</f>
+      <c r="G32" s="198"/>
+      <c r="H32" s="199"/>
+      <c r="I32" s="197" t="str">
+        <f>IF(I9="","",1100)</f>
         <v/>
       </c>
-      <c r="I15" s="88"/>
-      <c r="J15" s="89"/>
-      <c r="K15" s="90" t="str">
-        <f ca="1">IFERROR(IF(I17=0,"",DATEDIF($B$1,I17,"ｍ")),"")</f>
+      <c r="J32" s="198"/>
+      <c r="K32" s="199"/>
+      <c r="L32" s="197" t="str">
+        <f>IF(L9="","",1100)</f>
         <v/>
       </c>
-      <c r="L15" s="88"/>
-      <c r="M15" s="89"/>
-      <c r="N15" s="90" t="str">
-        <f ca="1">IFERROR(IF(L17=0,"",DATEDIF($B$1,L17,"ｍ")),"")</f>
+      <c r="M32" s="198"/>
+      <c r="N32" s="199"/>
+      <c r="O32" s="197" t="str">
+        <f>IF(O9="","",1100)</f>
         <v/>
       </c>
+      <c r="P32" s="198"/>
+      <c r="Q32" s="199"/>
+      <c r="R32" s="197" t="str">
+        <f>IF(R9="","",1100)</f>
+        <v/>
+      </c>
+      <c r="S32" s="198"/>
+      <c r="T32" s="199"/>
+      <c r="U32" s="197" t="str">
+        <f>IF(U9="","",1100)</f>
+        <v/>
+      </c>
+      <c r="V32" s="198"/>
+      <c r="W32" s="199"/>
+      <c r="AM32" s="154"/>
+      <c r="AN32" s="154"/>
+      <c r="AO32" s="154"/>
+      <c r="AP32" s="154"/>
+      <c r="AQ32" s="154"/>
+      <c r="AR32" s="154"/>
+      <c r="AS32" s="154"/>
+      <c r="AT32" s="154"/>
+      <c r="AU32" s="154"/>
+      <c r="AV32" s="154"/>
+      <c r="AW32" s="133"/>
+      <c r="AX32" s="133"/>
+      <c r="AY32" s="133"/>
+      <c r="AZ32" s="133"/>
+      <c r="BA32" s="133"/>
+      <c r="BB32" s="133"/>
+      <c r="BC32" s="133"/>
+      <c r="BD32" s="133"/>
+      <c r="BE32" s="133"/>
+      <c r="BF32" s="133"/>
+      <c r="BG32" s="133"/>
+      <c r="BH32" s="133"/>
+      <c r="BI32" s="163"/>
+      <c r="BJ32" s="163"/>
+      <c r="BK32" s="163"/>
+      <c r="BL32" s="163"/>
+      <c r="BM32" s="163"/>
+      <c r="BN32" s="163"/>
+      <c r="BO32" s="163"/>
+      <c r="BP32" s="163"/>
+      <c r="BQ32" s="163"/>
+      <c r="BR32" s="163"/>
+      <c r="BS32" s="163"/>
+      <c r="BT32" s="163"/>
+      <c r="BU32" s="163"/>
+      <c r="BV32" s="163"/>
+      <c r="BW32" s="163"/>
+      <c r="BX32" s="163"/>
+      <c r="BY32" s="163"/>
+      <c r="BZ32" s="163"/>
+      <c r="CA32" s="163"/>
+      <c r="CB32" s="163"/>
+      <c r="CC32" s="163"/>
+      <c r="CD32" s="163"/>
+      <c r="CE32" s="163"/>
+      <c r="CF32" s="163"/>
+      <c r="CG32" s="163"/>
+      <c r="CH32" s="163"/>
+      <c r="CI32" s="163"/>
+      <c r="CJ32" s="163"/>
+      <c r="CK32" s="163"/>
+      <c r="CL32" s="163"/>
+      <c r="CM32" s="163"/>
+      <c r="CN32" s="163"/>
+      <c r="CO32" s="163"/>
+      <c r="CP32" s="163"/>
+      <c r="CQ32" s="163"/>
+      <c r="CR32" s="163"/>
+      <c r="CS32" s="163"/>
+      <c r="CT32" s="163"/>
+      <c r="CU32" s="163"/>
+      <c r="CV32" s="163"/>
     </row>
-    <row r="16" spans="1:14" ht="26" customHeight="1">
-      <c r="A16" s="94"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="93"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="93"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="93"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="M16" s="93"/>
-      <c r="N16" s="91"/>
+    <row r="33" spans="1:100" ht="60" customHeight="1">
+      <c r="A33" s="60"/>
+      <c r="B33" s="196" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="197"/>
+      <c r="D33" s="198"/>
+      <c r="E33" s="199"/>
+      <c r="F33" s="197"/>
+      <c r="G33" s="198"/>
+      <c r="H33" s="199"/>
+      <c r="I33" s="197"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="199"/>
+      <c r="L33" s="197"/>
+      <c r="M33" s="198"/>
+      <c r="N33" s="199"/>
+      <c r="O33" s="197"/>
+      <c r="P33" s="198"/>
+      <c r="Q33" s="199"/>
+      <c r="R33" s="197"/>
+      <c r="S33" s="198"/>
+      <c r="T33" s="199"/>
+      <c r="U33" s="197"/>
+      <c r="V33" s="198"/>
+      <c r="W33" s="199"/>
+      <c r="X33" s="200" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y33" s="201"/>
+      <c r="Z33" s="202"/>
+      <c r="AM33" s="154"/>
+      <c r="AN33" s="154"/>
+      <c r="AO33" s="154"/>
+      <c r="AP33" s="154"/>
+      <c r="AQ33" s="154"/>
+      <c r="AR33" s="154"/>
+      <c r="AS33" s="154"/>
+      <c r="AT33" s="154"/>
+      <c r="AU33" s="154"/>
+      <c r="AV33" s="154"/>
+      <c r="AW33" s="133"/>
+      <c r="AX33" s="133"/>
+      <c r="AY33" s="133"/>
+      <c r="AZ33" s="133"/>
+      <c r="BA33" s="133"/>
+      <c r="BB33" s="133"/>
+      <c r="BC33" s="133"/>
+      <c r="BD33" s="133"/>
+      <c r="BE33" s="133"/>
+      <c r="BF33" s="133"/>
+      <c r="BG33" s="133"/>
+      <c r="BH33" s="133"/>
+      <c r="BI33" s="163"/>
+      <c r="BJ33" s="163"/>
+      <c r="BK33" s="163"/>
+      <c r="BL33" s="163"/>
+      <c r="BM33" s="163"/>
+      <c r="BN33" s="163"/>
+      <c r="BO33" s="163"/>
+      <c r="BP33" s="163"/>
+      <c r="BQ33" s="163"/>
+      <c r="BR33" s="163"/>
+      <c r="BS33" s="163"/>
+      <c r="BT33" s="163"/>
+      <c r="BU33" s="163"/>
+      <c r="BV33" s="163"/>
+      <c r="BW33" s="163"/>
+      <c r="BX33" s="163"/>
+      <c r="BY33" s="163"/>
+      <c r="BZ33" s="163"/>
+      <c r="CA33" s="163"/>
+      <c r="CB33" s="163"/>
+      <c r="CC33" s="163"/>
+      <c r="CD33" s="163"/>
+      <c r="CE33" s="163"/>
+      <c r="CF33" s="163"/>
+      <c r="CG33" s="163"/>
+      <c r="CH33" s="163"/>
+      <c r="CI33" s="163"/>
+      <c r="CJ33" s="163"/>
+      <c r="CK33" s="163"/>
+      <c r="CL33" s="163"/>
+      <c r="CM33" s="163"/>
+      <c r="CN33" s="163"/>
+      <c r="CO33" s="163"/>
+      <c r="CP33" s="163"/>
+      <c r="CQ33" s="163"/>
+      <c r="CR33" s="163"/>
+      <c r="CS33" s="163"/>
+      <c r="CT33" s="163"/>
+      <c r="CU33" s="163"/>
+      <c r="CV33" s="163"/>
     </row>
-    <row r="17" spans="1:14" ht="21" thickBot="1">
-      <c r="A17" s="95"/>
-      <c r="B17" s="100"/>
-      <c r="C17" s="43" t="str">
-        <f>IF(C15&lt;&gt;"", EDATE(C15, IF(B1="アプラス", 25*12, 35*12)), "")</f>
+    <row r="34" spans="1:100" ht="60" customHeight="1" thickBot="1">
+      <c r="A34" s="60"/>
+      <c r="B34" s="203" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="D34" s="205"/>
+      <c r="E34" s="206">
+        <f>IFERROR(C34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="F34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="G34" s="205"/>
+      <c r="H34" s="206">
+        <f>IFERROR(F34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="I34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="J34" s="205"/>
+      <c r="K34" s="206">
+        <f>IFERROR(I34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="L34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="M34" s="205"/>
+      <c r="N34" s="206">
+        <f>IFERROR(L34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="O34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="P34" s="205"/>
+      <c r="Q34" s="206">
+        <f>IFERROR(O34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="R34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="S34" s="205"/>
+      <c r="T34" s="206">
+        <f>IFERROR(R34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="U34" s="204">
+        <v>60000</v>
+      </c>
+      <c r="V34" s="205"/>
+      <c r="W34" s="206">
+        <f>IFERROR(U34/12,"")</f>
+        <v>5000</v>
+      </c>
+      <c r="X34" s="207"/>
+      <c r="Y34" s="208"/>
+      <c r="Z34" s="209"/>
+      <c r="AM34" s="154"/>
+      <c r="AN34" s="154"/>
+      <c r="AO34" s="154"/>
+      <c r="AP34" s="154"/>
+      <c r="AQ34" s="154"/>
+      <c r="AR34" s="154"/>
+      <c r="AS34" s="154"/>
+      <c r="AT34" s="154"/>
+      <c r="AU34" s="154"/>
+      <c r="AV34" s="154"/>
+      <c r="AW34" s="133"/>
+      <c r="AX34" s="133"/>
+      <c r="AY34" s="133"/>
+      <c r="AZ34" s="133"/>
+      <c r="BA34" s="133"/>
+      <c r="BB34" s="133"/>
+      <c r="BC34" s="133"/>
+      <c r="BD34" s="133"/>
+      <c r="BE34" s="133"/>
+      <c r="BF34" s="133"/>
+      <c r="BG34" s="133"/>
+      <c r="BH34" s="133"/>
+      <c r="BI34" s="163"/>
+      <c r="BJ34" s="163"/>
+      <c r="BK34" s="163"/>
+      <c r="BL34" s="163"/>
+      <c r="BM34" s="163"/>
+      <c r="BN34" s="163"/>
+      <c r="BO34" s="163"/>
+      <c r="BP34" s="163"/>
+      <c r="BQ34" s="163"/>
+      <c r="BR34" s="163"/>
+      <c r="BS34" s="163"/>
+      <c r="BT34" s="163"/>
+      <c r="BU34" s="163"/>
+      <c r="BV34" s="163"/>
+      <c r="BW34" s="163"/>
+      <c r="BX34" s="163"/>
+      <c r="BY34" s="163"/>
+      <c r="BZ34" s="163"/>
+      <c r="CA34" s="163"/>
+      <c r="CB34" s="163"/>
+      <c r="CC34" s="163"/>
+      <c r="CD34" s="163"/>
+      <c r="CE34" s="163"/>
+      <c r="CF34" s="163"/>
+      <c r="CG34" s="163"/>
+      <c r="CH34" s="163"/>
+      <c r="CI34" s="163"/>
+      <c r="CJ34" s="163"/>
+      <c r="CK34" s="163"/>
+      <c r="CL34" s="163"/>
+      <c r="CM34" s="163"/>
+      <c r="CN34" s="163"/>
+      <c r="CO34" s="163"/>
+      <c r="CP34" s="163"/>
+      <c r="CQ34" s="163"/>
+      <c r="CR34" s="163"/>
+      <c r="CS34" s="163"/>
+      <c r="CT34" s="163"/>
+      <c r="CU34" s="163"/>
+      <c r="CV34" s="163"/>
+    </row>
+    <row r="35" spans="1:100" ht="75" customHeight="1" thickTop="1" thickBot="1">
+      <c r="A35" s="210" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="211" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="212">
+        <f>IFERROR(IF(D26-SUM(C27:C33)-E34=0,"",D26-SUM(C27:C33)-E34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="D35" s="213"/>
+      <c r="E35" s="214"/>
+      <c r="F35" s="215">
+        <f>IFERROR(IF(G26-SUM(F27:F33)-H34=0,"",G26-SUM(F27:F33)-H34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="G35" s="216"/>
+      <c r="H35" s="217"/>
+      <c r="I35" s="215">
+        <f>IFERROR(IF(J26-SUM(I27:I33)-K34=0,"",J26-SUM(I27:I33)-K34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="J35" s="216"/>
+      <c r="K35" s="217"/>
+      <c r="L35" s="215">
+        <f>IFERROR(IF(M26-SUM(L27:L33)-N34=0,"",M26-SUM(L27:L33)-N34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="M35" s="216"/>
+      <c r="N35" s="217"/>
+      <c r="O35" s="215">
+        <f>IFERROR(IF(P26-SUM(O27:O33)-Q34=0,"",P26-SUM(O27:O33)-Q34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="P35" s="216"/>
+      <c r="Q35" s="217"/>
+      <c r="R35" s="215">
+        <f>IFERROR(IF(S26-SUM(R27:R33)-T34=0,"",S26-SUM(R27:R33)-T34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="S35" s="216"/>
+      <c r="T35" s="217"/>
+      <c r="U35" s="215">
+        <f>IFERROR(IF(V26-SUM(U27:U33)-W34=0,"",V26-SUM(U27:U33)-W34),"")</f>
+        <v>-5000</v>
+      </c>
+      <c r="V35" s="216"/>
+      <c r="W35" s="217"/>
+      <c r="X35" s="218">
+        <f>SUM(C35:W35)</f>
+        <v>-35000</v>
+      </c>
+      <c r="Y35" s="219"/>
+      <c r="Z35" s="220"/>
+      <c r="AM35" s="154"/>
+      <c r="AN35" s="154"/>
+      <c r="AO35" s="154"/>
+      <c r="AP35" s="154"/>
+      <c r="AQ35" s="154"/>
+      <c r="AR35" s="154"/>
+      <c r="AS35" s="154"/>
+      <c r="AT35" s="154"/>
+      <c r="AU35" s="154"/>
+      <c r="AV35" s="154"/>
+      <c r="AW35" s="133"/>
+      <c r="AX35" s="133"/>
+      <c r="AY35" s="133"/>
+      <c r="AZ35" s="133"/>
+      <c r="BA35" s="133"/>
+      <c r="BB35" s="133"/>
+      <c r="BC35" s="133"/>
+      <c r="BD35" s="133"/>
+      <c r="BE35" s="133"/>
+      <c r="BF35" s="133"/>
+      <c r="BG35" s="133"/>
+      <c r="BH35" s="133"/>
+      <c r="BI35" s="163"/>
+      <c r="BJ35" s="163"/>
+      <c r="BK35" s="163"/>
+      <c r="BL35" s="163"/>
+      <c r="BM35" s="163"/>
+      <c r="BN35" s="163"/>
+      <c r="BO35" s="163"/>
+      <c r="BP35" s="163"/>
+      <c r="BQ35" s="163"/>
+      <c r="BR35" s="163"/>
+      <c r="BS35" s="163"/>
+      <c r="BT35" s="163"/>
+      <c r="BU35" s="163"/>
+      <c r="BV35" s="163"/>
+      <c r="BW35" s="163"/>
+      <c r="BX35" s="163"/>
+      <c r="BY35" s="163"/>
+      <c r="BZ35" s="163"/>
+      <c r="CA35" s="163"/>
+      <c r="CB35" s="163"/>
+      <c r="CC35" s="163"/>
+      <c r="CD35" s="163"/>
+      <c r="CE35" s="163"/>
+      <c r="CF35" s="163"/>
+      <c r="CG35" s="163"/>
+      <c r="CH35" s="163"/>
+      <c r="CI35" s="163"/>
+      <c r="CJ35" s="163"/>
+      <c r="CK35" s="163"/>
+      <c r="CL35" s="163"/>
+      <c r="CM35" s="163"/>
+      <c r="CN35" s="163"/>
+      <c r="CO35" s="163"/>
+      <c r="CP35" s="163"/>
+      <c r="CQ35" s="163"/>
+      <c r="CR35" s="163"/>
+      <c r="CS35" s="163"/>
+      <c r="CT35" s="163"/>
+      <c r="CU35" s="163"/>
+      <c r="CV35" s="163"/>
+    </row>
+    <row r="36" spans="1:100" ht="75" customHeight="1" thickBot="1">
+      <c r="A36" s="221"/>
+      <c r="B36" s="222" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="223">
+        <f>IF(C35="","",C35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="D36" s="224"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="223">
+        <f>IF(F35="","",F35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="G36" s="224"/>
+      <c r="H36" s="225"/>
+      <c r="I36" s="223">
+        <f>IF(I35="","",I35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="J36" s="224"/>
+      <c r="K36" s="225"/>
+      <c r="L36" s="223">
+        <f>IF(L35="","",L35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="M36" s="224"/>
+      <c r="N36" s="225"/>
+      <c r="O36" s="223">
+        <f>IF(O35="","",O35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="P36" s="224"/>
+      <c r="Q36" s="225"/>
+      <c r="R36" s="223">
+        <f>IF(R35="","",R35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="S36" s="224"/>
+      <c r="T36" s="225"/>
+      <c r="U36" s="223">
+        <f>IF(U35="","",U35*12)</f>
+        <v>-60000</v>
+      </c>
+      <c r="V36" s="224"/>
+      <c r="W36" s="225"/>
+      <c r="X36" s="218">
+        <f>SUM(C36:W36)</f>
+        <v>-420000</v>
+      </c>
+      <c r="Y36" s="219"/>
+      <c r="Z36" s="220"/>
+      <c r="AW36" s="41"/>
+      <c r="AX36" s="41"/>
+      <c r="AY36" s="41"/>
+      <c r="AZ36" s="41"/>
+      <c r="BA36" s="41"/>
+      <c r="BB36" s="41"/>
+      <c r="BC36" s="41"/>
+      <c r="BD36" s="41"/>
+      <c r="BE36" s="41"/>
+      <c r="BF36" s="41"/>
+      <c r="BG36" s="41"/>
+      <c r="BH36" s="41"/>
+      <c r="BI36" s="41"/>
+      <c r="BJ36" s="41"/>
+      <c r="BK36" s="41"/>
+      <c r="BL36" s="41"/>
+      <c r="BM36" s="41"/>
+      <c r="BN36" s="41"/>
+      <c r="BO36" s="41"/>
+      <c r="BP36" s="41"/>
+      <c r="BQ36" s="41"/>
+      <c r="BR36" s="41"/>
+      <c r="BS36" s="41"/>
+      <c r="BT36" s="41"/>
+      <c r="BU36" s="41"/>
+      <c r="BV36" s="41"/>
+      <c r="BW36" s="41"/>
+      <c r="BX36" s="41"/>
+      <c r="BY36" s="41"/>
+      <c r="BZ36" s="41"/>
+      <c r="CA36" s="41"/>
+      <c r="CB36" s="41"/>
+      <c r="CC36" s="41"/>
+      <c r="CD36" s="41"/>
+      <c r="CE36" s="41"/>
+      <c r="CF36" s="41"/>
+      <c r="CG36" s="41"/>
+      <c r="CH36" s="41"/>
+      <c r="CI36" s="41"/>
+      <c r="CJ36" s="41"/>
+      <c r="CK36" s="41"/>
+      <c r="CL36" s="41"/>
+      <c r="CM36" s="41"/>
+      <c r="CN36" s="41"/>
+      <c r="CO36" s="41"/>
+      <c r="CP36" s="41"/>
+      <c r="CQ36" s="41"/>
+      <c r="CR36" s="41"/>
+      <c r="CS36" s="41"/>
+      <c r="CT36" s="41"/>
+      <c r="CU36" s="41"/>
+      <c r="CV36" s="41"/>
+    </row>
+    <row r="37" spans="1:100" ht="94.5" customHeight="1" thickBot="1">
+      <c r="A37" s="226"/>
+      <c r="B37" s="227" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="228" t="str">
+        <f>IF(OR(C35="",E23=""),"",C35*E23)</f>
         <v/>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="15" t="str">
-        <f>IF(C15=0,"",DATEDIF(C15,C17,"y"))</f>
+      <c r="D37" s="229"/>
+      <c r="E37" s="230"/>
+      <c r="F37" s="228" t="str">
+        <f>IF(OR(F35="",H23=""),"",F35*H23)</f>
         <v/>
       </c>
-      <c r="F17" s="43" t="str">
-        <f>IF(F15&lt;&gt;"", EDATE(F15, IF(E1="アプラス", 25*12, 35*12)), "")</f>
+      <c r="G37" s="229"/>
+      <c r="H37" s="230"/>
+      <c r="I37" s="228" t="str">
+        <f>IF(OR(I35="",K23=""),"",I35*K23)</f>
         <v/>
       </c>
-      <c r="G17" s="44"/>
-      <c r="H17" s="15" t="str">
-        <f>IF(F15=0,"",DATEDIF(F15,F17,"y"))</f>
+      <c r="J37" s="229"/>
+      <c r="K37" s="230"/>
+      <c r="L37" s="228" t="str">
+        <f>IF(OR(L35="",N23=""),"",L35*N23)</f>
         <v/>
       </c>
-      <c r="I17" s="43" t="str">
-        <f>IF(I15&lt;&gt;"", EDATE(I15, IF(H1="アプラス", 25*12, 35*12)), "")</f>
+      <c r="M37" s="229"/>
+      <c r="N37" s="230"/>
+      <c r="O37" s="228" t="str">
+        <f>IF(OR(O35="",Q23=""),"",O35*Q23)</f>
         <v/>
       </c>
-      <c r="J17" s="44"/>
-      <c r="K17" s="15" t="str">
-        <f>IF(I15=0,"",DATEDIF(I15,I17,"y"))</f>
+      <c r="P37" s="229"/>
+      <c r="Q37" s="230"/>
+      <c r="R37" s="228" t="str">
+        <f>IF(OR(R35="",T23=""),"",R35*T23)</f>
         <v/>
       </c>
-      <c r="L17" s="43" t="str">
-        <f>IF(L15&lt;&gt;"", EDATE(L15, IF(K1="アプラス", 25*12, 35*12)), "")</f>
+      <c r="S37" s="229"/>
+      <c r="T37" s="230"/>
+      <c r="U37" s="228" t="str">
+        <f>IF(OR(U35="",W23=""),"",U35*W23)</f>
         <v/>
       </c>
-      <c r="M17" s="44"/>
-      <c r="N17" s="15" t="str">
-        <f>IF(L15=0,"",DATEDIF(L15,L17,"y"))</f>
+      <c r="V37" s="229"/>
+      <c r="W37" s="230"/>
+      <c r="X37" s="231">
+        <f>SUM(C37:W37)</f>
+        <v>0</v>
+      </c>
+      <c r="Y37" s="232"/>
+      <c r="Z37" s="233"/>
+      <c r="AW37" s="41"/>
+      <c r="AX37" s="41"/>
+      <c r="AY37" s="41"/>
+      <c r="AZ37" s="41"/>
+      <c r="BA37" s="41"/>
+      <c r="BB37" s="41"/>
+      <c r="BC37" s="41"/>
+      <c r="BD37" s="41"/>
+      <c r="BE37" s="41"/>
+      <c r="BF37" s="41"/>
+      <c r="BG37" s="41"/>
+      <c r="BH37" s="41"/>
+      <c r="BI37" s="41"/>
+      <c r="BJ37" s="41"/>
+      <c r="BK37" s="41"/>
+      <c r="BL37" s="41"/>
+      <c r="BM37" s="41"/>
+      <c r="BN37" s="41"/>
+      <c r="BO37" s="41"/>
+      <c r="BP37" s="41"/>
+      <c r="BQ37" s="41"/>
+      <c r="BR37" s="41"/>
+      <c r="BS37" s="41"/>
+      <c r="BT37" s="41"/>
+      <c r="BU37" s="41"/>
+      <c r="BV37" s="41"/>
+      <c r="BW37" s="41"/>
+      <c r="BX37" s="41"/>
+      <c r="BY37" s="41"/>
+      <c r="BZ37" s="41"/>
+      <c r="CA37" s="41"/>
+      <c r="CB37" s="41"/>
+      <c r="CC37" s="41"/>
+      <c r="CD37" s="41"/>
+      <c r="CE37" s="41"/>
+      <c r="CF37" s="41"/>
+      <c r="CG37" s="41"/>
+      <c r="CH37" s="41"/>
+      <c r="CI37" s="41"/>
+      <c r="CJ37" s="41"/>
+      <c r="CK37" s="41"/>
+      <c r="CL37" s="41"/>
+      <c r="CM37" s="41"/>
+      <c r="CN37" s="41"/>
+      <c r="CO37" s="41"/>
+      <c r="CP37" s="41"/>
+      <c r="CQ37" s="41"/>
+      <c r="CR37" s="41"/>
+      <c r="CS37" s="41"/>
+      <c r="CT37" s="41"/>
+      <c r="CU37" s="41"/>
+      <c r="CV37" s="41"/>
+    </row>
+    <row r="38" spans="1:100" ht="51" customHeight="1" thickTop="1">
+      <c r="F38" s="234"/>
+      <c r="G38" s="234"/>
+      <c r="H38" s="234"/>
+      <c r="I38" s="234"/>
+      <c r="J38" s="234"/>
+      <c r="K38" s="234"/>
+      <c r="L38" s="234"/>
+      <c r="M38" s="234"/>
+      <c r="N38" s="234"/>
+      <c r="O38" s="234"/>
+      <c r="P38" s="234"/>
+      <c r="Q38" s="234"/>
+      <c r="R38" s="234"/>
+      <c r="S38" s="234"/>
+      <c r="T38" s="234"/>
+      <c r="U38" s="234"/>
+      <c r="V38" s="234"/>
+      <c r="W38" s="234"/>
+    </row>
+    <row r="39" spans="1:100" ht="51" customHeight="1">
+      <c r="C39" s="235" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="234"/>
+      <c r="K39" s="234"/>
+      <c r="L39" s="234"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="234"/>
+      <c r="O39" s="234"/>
+      <c r="P39" s="234"/>
+      <c r="Q39" s="234"/>
+      <c r="R39" s="234"/>
+      <c r="S39" s="234"/>
+      <c r="T39" s="234"/>
+      <c r="U39" s="234"/>
+      <c r="V39" s="234"/>
+      <c r="W39" s="234"/>
+    </row>
+    <row r="40" spans="1:100" ht="51" customHeight="1">
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="234"/>
+      <c r="O40" s="234"/>
+      <c r="P40" s="234"/>
+      <c r="Q40" s="234"/>
+      <c r="R40" s="234"/>
+      <c r="S40" s="234"/>
+      <c r="T40" s="234"/>
+      <c r="U40" s="234"/>
+      <c r="V40" s="234"/>
+      <c r="W40" s="234"/>
+    </row>
+    <row r="41" spans="1:100" ht="51" customHeight="1">
+      <c r="C41" s="8" t="str">
+        <f>IF(C9="","",(D26-C30-C31)*12)</f>
         <v/>
       </c>
+      <c r="D41" s="236"/>
+      <c r="E41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(C41/D41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="8" t="str">
+        <f>IF(F9="","",(G26-F30-F31)*12)</f>
+        <v/>
+      </c>
+      <c r="G41" s="236"/>
+      <c r="H41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(F41/G41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="8" t="str">
+        <f>IF(I9="","",(J26-I30-I31)*12)</f>
+        <v/>
+      </c>
+      <c r="J41" s="236"/>
+      <c r="K41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(I41/J41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="L41" s="8" t="str">
+        <f>IF(L9="","",(M26-L30-L31)*12)</f>
+        <v/>
+      </c>
+      <c r="M41" s="236"/>
+      <c r="N41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(L41/M41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="O41" s="8" t="str">
+        <f>IF(O9="","",(P26-O30-O31)*12)</f>
+        <v/>
+      </c>
+      <c r="P41" s="236"/>
+      <c r="Q41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(O41/P41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="R41" s="8" t="str">
+        <f>IF(R9="","",(S26-R30-R31)*12)</f>
+        <v/>
+      </c>
+      <c r="S41" s="236"/>
+      <c r="T41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(R41/S41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="U41" s="8" t="str">
+        <f>IF(U9="","",(V26-U30-U31)*12)</f>
+        <v/>
+      </c>
+      <c r="V41" s="236"/>
+      <c r="W41" s="237" t="str">
+        <f>IFERROR(ROUNDDOWN(U41/V41/10000,1),"")</f>
+        <v/>
+      </c>
+      <c r="AW41" s="41"/>
+      <c r="AX41" s="41"/>
+      <c r="AY41" s="41"/>
+      <c r="AZ41" s="41"/>
+      <c r="BA41" s="41"/>
+      <c r="BB41" s="41"/>
+      <c r="BC41" s="41"/>
+      <c r="BD41" s="41"/>
+      <c r="BE41" s="41"/>
+      <c r="BF41" s="41"/>
+      <c r="BG41" s="41"/>
+      <c r="BH41" s="41"/>
+      <c r="BI41" s="41"/>
+      <c r="BJ41" s="41"/>
+      <c r="BK41" s="41"/>
+      <c r="BL41" s="41"/>
+      <c r="BM41" s="41"/>
+      <c r="BN41" s="41"/>
+      <c r="BO41" s="41"/>
+      <c r="BP41" s="41"/>
+      <c r="BQ41" s="41"/>
+      <c r="BR41" s="41"/>
+      <c r="BS41" s="41"/>
+      <c r="BT41" s="41"/>
+      <c r="BU41" s="41"/>
+      <c r="BV41" s="41"/>
+      <c r="BW41" s="41"/>
+      <c r="BX41" s="41"/>
+      <c r="BY41" s="41"/>
+      <c r="BZ41" s="41"/>
+      <c r="CA41" s="41"/>
+      <c r="CB41" s="41"/>
+      <c r="CC41" s="41"/>
+      <c r="CD41" s="41"/>
+      <c r="CE41" s="41"/>
+      <c r="CF41" s="41"/>
+      <c r="CG41" s="41"/>
+      <c r="CH41" s="41"/>
+      <c r="CI41" s="41"/>
+      <c r="CJ41" s="41"/>
+      <c r="CK41" s="41"/>
+      <c r="CL41" s="41"/>
+      <c r="CM41" s="41"/>
+      <c r="CN41" s="41"/>
+      <c r="CO41" s="41"/>
+      <c r="CP41" s="41"/>
+      <c r="CQ41" s="41"/>
+      <c r="CR41" s="41"/>
+      <c r="CS41" s="41"/>
+      <c r="CT41" s="41"/>
+      <c r="CU41" s="41"/>
+      <c r="CV41" s="41"/>
     </row>
-    <row r="18" spans="1:14" ht="42" thickTop="1" thickBot="1">
-      <c r="A18" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="17" t="s">
+    <row r="42" spans="1:100" ht="51" customHeight="1">
+      <c r="F42" s="234"/>
+      <c r="G42" s="234"/>
+      <c r="H42" s="234"/>
+      <c r="I42" s="234"/>
+      <c r="J42" s="234"/>
+      <c r="K42" s="234"/>
+      <c r="L42" s="234"/>
+      <c r="M42" s="234"/>
+      <c r="N42" s="234"/>
+      <c r="O42" s="234"/>
+      <c r="P42" s="234"/>
+      <c r="Q42" s="234"/>
+      <c r="R42" s="234"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="234"/>
+      <c r="U42" s="234"/>
+      <c r="V42" s="234"/>
+      <c r="W42" s="234"/>
+    </row>
+    <row r="43" spans="1:100" ht="51" customHeight="1" thickBot="1"/>
+    <row r="44" spans="1:100" ht="50" customHeight="1">
+      <c r="A44" s="238" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="238"/>
+      <c r="C44" s="239">
+        <f>C9</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="240"/>
+      <c r="E44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="F44" s="239">
+        <f>F9</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="240"/>
+      <c r="H44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" s="239">
+        <f>I9</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="240"/>
+      <c r="K44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="L44" s="239">
+        <f>L9</f>
+        <v>0</v>
+      </c>
+      <c r="M44" s="240"/>
+      <c r="N44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="O44" s="239">
+        <f>O9</f>
+        <v>0</v>
+      </c>
+      <c r="P44" s="240"/>
+      <c r="Q44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="R44" s="239">
+        <f>R9</f>
+        <v>0</v>
+      </c>
+      <c r="S44" s="240"/>
+      <c r="T44" s="241" t="s">
+        <v>56</v>
+      </c>
+      <c r="U44" s="239">
+        <f>U9</f>
+        <v>0</v>
+      </c>
+      <c r="V44" s="240"/>
+      <c r="W44" s="241" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:100" ht="50" customHeight="1">
+      <c r="B45" s="8"/>
+      <c r="C45" s="242" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="45"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="46"/>
+      <c r="D45" s="243"/>
+      <c r="E45" s="244"/>
+      <c r="F45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="243"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="J45" s="243"/>
+      <c r="K45" s="244"/>
+      <c r="L45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="M45" s="243"/>
+      <c r="N45" s="244"/>
+      <c r="O45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="P45" s="243"/>
+      <c r="Q45" s="244"/>
+      <c r="R45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="S45" s="243"/>
+      <c r="T45" s="244"/>
+      <c r="U45" s="242" t="s">
+        <v>14</v>
+      </c>
+      <c r="V45" s="243"/>
+      <c r="W45" s="244"/>
     </row>
-    <row r="19" spans="1:14" ht="21" customHeight="1" thickTop="1">
-      <c r="A19" s="19"/>
-      <c r="B19" s="105" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="48"/>
-      <c r="K19" s="49"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="49"/>
+    <row r="46" spans="1:100" ht="50" customHeight="1">
+      <c r="B46" s="8"/>
+      <c r="C46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="243"/>
+      <c r="E46" s="244"/>
+      <c r="F46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="243"/>
+      <c r="H46" s="244"/>
+      <c r="I46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="J46" s="243"/>
+      <c r="K46" s="244"/>
+      <c r="L46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="243"/>
+      <c r="N46" s="244"/>
+      <c r="O46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="P46" s="243"/>
+      <c r="Q46" s="244"/>
+      <c r="R46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="S46" s="243"/>
+      <c r="T46" s="244"/>
+      <c r="U46" s="242" t="s">
+        <v>57</v>
+      </c>
+      <c r="V46" s="243"/>
+      <c r="W46" s="244"/>
     </row>
-    <row r="20" spans="1:14" ht="20" customHeight="1">
-      <c r="A20" s="19"/>
-      <c r="B20" s="106"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="51"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="52"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="50"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="52"/>
+    <row r="47" spans="1:100" ht="50" customHeight="1">
+      <c r="B47" s="8"/>
+      <c r="C47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" s="243" t="e">
+        <f>D46/E47*E11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E47" s="245"/>
+      <c r="F47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47" s="243" t="e">
+        <f>G46/H47*H11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H47" s="245"/>
+      <c r="I47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="J47" s="243" t="e">
+        <f>J46/K47*K11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K47" s="245"/>
+      <c r="L47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="M47" s="243" t="e">
+        <f>M46/N47*N11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N47" s="245"/>
+      <c r="O47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="P47" s="243" t="e">
+        <f>P46/Q47*Q11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q47" s="245"/>
+      <c r="R47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="S47" s="243" t="e">
+        <f>S46/T47*T11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T47" s="245"/>
+      <c r="U47" s="242" t="s">
+        <v>58</v>
+      </c>
+      <c r="V47" s="243" t="e">
+        <f>V46/W47*W11</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W47" s="245"/>
     </row>
-    <row r="21" spans="1:14" ht="20" customHeight="1">
-      <c r="A21" s="19"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="54"/>
-      <c r="H21" s="55"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="54"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="54"/>
-      <c r="N21" s="55"/>
+    <row r="48" spans="1:100" ht="51" customHeight="1" thickBot="1">
+      <c r="C48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="D48" s="247"/>
+      <c r="E48" s="248"/>
+      <c r="F48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" s="247"/>
+      <c r="H48" s="248"/>
+      <c r="I48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="J48" s="247"/>
+      <c r="K48" s="248"/>
+      <c r="L48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="M48" s="247"/>
+      <c r="N48" s="248"/>
+      <c r="O48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="P48" s="247"/>
+      <c r="Q48" s="248"/>
+      <c r="R48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="S48" s="247"/>
+      <c r="T48" s="248"/>
+      <c r="U48" s="246" t="s">
+        <v>59</v>
+      </c>
+      <c r="V48" s="247"/>
+      <c r="W48" s="248"/>
     </row>
-    <row r="22" spans="1:14" ht="24">
-      <c r="A22" s="94" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="56"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="58"/>
+    <row r="49" spans="1:23" ht="51" customHeight="1">
+      <c r="C49" s="249"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="249"/>
+      <c r="G49" s="250"/>
+      <c r="H49" s="250"/>
+      <c r="I49" s="249"/>
+      <c r="J49" s="250"/>
+      <c r="K49" s="250"/>
+      <c r="L49" s="249"/>
+      <c r="M49" s="234"/>
+      <c r="N49" s="234"/>
+      <c r="O49" s="249"/>
+      <c r="P49" s="250"/>
+      <c r="Q49" s="250"/>
+      <c r="R49" s="249"/>
+      <c r="S49" s="250"/>
+      <c r="T49" s="250"/>
+      <c r="U49" s="249"/>
+      <c r="V49" s="234"/>
+      <c r="W49" s="234"/>
     </row>
-    <row r="23" spans="1:14" ht="24">
-      <c r="A23" s="94"/>
-      <c r="B23" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="56"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="58"/>
+    <row r="50" spans="1:23" ht="51" customHeight="1" thickBot="1">
+      <c r="C50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="16"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="250"/>
+      <c r="H50" s="250"/>
+      <c r="I50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="J50" s="250"/>
+      <c r="K50" s="250"/>
+      <c r="L50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="M50" s="234"/>
+      <c r="N50" s="234"/>
+      <c r="O50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="P50" s="250"/>
+      <c r="Q50" s="250"/>
+      <c r="R50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="S50" s="250"/>
+      <c r="T50" s="250"/>
+      <c r="U50" s="249" t="s">
+        <v>56</v>
+      </c>
+      <c r="V50" s="234"/>
+      <c r="W50" s="234"/>
     </row>
-    <row r="24" spans="1:14" ht="24">
-      <c r="A24" s="94"/>
-      <c r="B24" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="33"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="33"/>
-      <c r="N24" s="34"/>
+    <row r="51" spans="1:23" ht="51" customHeight="1">
+      <c r="A51" s="238" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="238"/>
+      <c r="C51" s="251"/>
+      <c r="D51" s="252"/>
+      <c r="E51" s="253"/>
+      <c r="F51" s="251"/>
+      <c r="G51" s="252"/>
+      <c r="H51" s="253"/>
+      <c r="I51" s="251"/>
+      <c r="J51" s="252"/>
+      <c r="K51" s="253"/>
+      <c r="L51" s="251"/>
+      <c r="M51" s="252"/>
+      <c r="N51" s="253"/>
+      <c r="O51" s="251"/>
+      <c r="P51" s="252"/>
+      <c r="Q51" s="253"/>
+      <c r="R51" s="251"/>
+      <c r="S51" s="252"/>
+      <c r="T51" s="253"/>
+      <c r="U51" s="251"/>
+      <c r="V51" s="252"/>
+      <c r="W51" s="253"/>
     </row>
-    <row r="25" spans="1:14" ht="24">
-      <c r="A25" s="94"/>
-      <c r="B25" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="32"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="34"/>
+    <row r="52" spans="1:23" ht="51" customHeight="1">
+      <c r="C52" s="254">
+        <f>C51+40</f>
+        <v>40</v>
+      </c>
+      <c r="D52" s="255"/>
+      <c r="E52" s="256"/>
+      <c r="F52" s="254">
+        <f>F51+40</f>
+        <v>40</v>
+      </c>
+      <c r="G52" s="255"/>
+      <c r="H52" s="256"/>
+      <c r="I52" s="254">
+        <f>I51+40</f>
+        <v>40</v>
+      </c>
+      <c r="J52" s="255"/>
+      <c r="K52" s="256"/>
+      <c r="L52" s="254">
+        <f>L51+40</f>
+        <v>40</v>
+      </c>
+      <c r="M52" s="255"/>
+      <c r="N52" s="256"/>
+      <c r="O52" s="254">
+        <f>O51+40</f>
+        <v>40</v>
+      </c>
+      <c r="P52" s="255"/>
+      <c r="Q52" s="256"/>
+      <c r="R52" s="254">
+        <f>R51+40</f>
+        <v>40</v>
+      </c>
+      <c r="S52" s="255"/>
+      <c r="T52" s="256"/>
+      <c r="U52" s="254">
+        <f>U51+40</f>
+        <v>40</v>
+      </c>
+      <c r="V52" s="255"/>
+      <c r="W52" s="256"/>
     </row>
-    <row r="26" spans="1:14" ht="25" thickBot="1">
-      <c r="A26" s="94"/>
-      <c r="B26" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" s="35" t="str">
-        <f>IF(C1="","",59000)</f>
+    <row r="53" spans="1:23" ht="51" customHeight="1" thickBot="1">
+      <c r="C53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="258">
+        <f>D51-D52</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="259"/>
+      <c r="F53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53" s="258">
+        <f>G51-G52</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="259"/>
+      <c r="I53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="J53" s="258">
+        <f>J51-J52</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="259"/>
+      <c r="L53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="M53" s="258">
+        <f>M51-M52</f>
+        <v>0</v>
+      </c>
+      <c r="N53" s="259"/>
+      <c r="O53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="P53" s="258">
+        <f>P51-P52</f>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="259"/>
+      <c r="R53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="S53" s="258">
+        <f>S51-S52</f>
+        <v>0</v>
+      </c>
+      <c r="T53" s="259"/>
+      <c r="U53" s="257" t="s">
+        <v>61</v>
+      </c>
+      <c r="V53" s="258">
+        <f>V51-V52</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="259"/>
+    </row>
+    <row r="54" spans="1:23" ht="51" customHeight="1">
+      <c r="C54" s="249"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="249"/>
+      <c r="G54" s="250"/>
+      <c r="H54" s="250"/>
+      <c r="I54" s="249"/>
+      <c r="J54" s="250"/>
+      <c r="K54" s="250"/>
+      <c r="L54" s="249"/>
+      <c r="M54" s="234"/>
+      <c r="N54" s="234"/>
+      <c r="O54" s="249"/>
+      <c r="P54" s="250"/>
+      <c r="Q54" s="250"/>
+      <c r="R54" s="249"/>
+      <c r="S54" s="250"/>
+      <c r="T54" s="250"/>
+      <c r="U54" s="249"/>
+      <c r="V54" s="234"/>
+      <c r="W54" s="234"/>
+    </row>
+    <row r="55" spans="1:23" ht="50" customHeight="1" thickBot="1">
+      <c r="B55" s="234"/>
+      <c r="C55" s="260">
+        <f>C18</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="261"/>
+      <c r="E55" s="234"/>
+      <c r="F55" s="260">
+        <f>F18</f>
+        <v>0</v>
+      </c>
+      <c r="G55" s="261"/>
+      <c r="H55" s="234"/>
+      <c r="I55" s="260">
+        <f>I18</f>
+        <v>0</v>
+      </c>
+      <c r="J55" s="261"/>
+      <c r="K55" s="234"/>
+      <c r="L55" s="260">
+        <f>L18</f>
+        <v>0</v>
+      </c>
+      <c r="M55" s="261"/>
+      <c r="N55" s="234"/>
+      <c r="O55" s="260">
+        <f>O18</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="261"/>
+      <c r="Q55" s="234"/>
+      <c r="R55" s="260">
+        <f>R18</f>
+        <v>0</v>
+      </c>
+      <c r="S55" s="261"/>
+      <c r="T55" s="234"/>
+      <c r="U55" s="260">
+        <f>U18</f>
+        <v>0</v>
+      </c>
+      <c r="V55" s="261"/>
+      <c r="W55" s="234"/>
+    </row>
+    <row r="56" spans="1:23" ht="50" customHeight="1">
+      <c r="A56" s="262" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="262"/>
+      <c r="C56" s="263">
+        <f>D53</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="264"/>
+      <c r="E56" s="265"/>
+      <c r="F56" s="263">
+        <f>G53</f>
+        <v>0</v>
+      </c>
+      <c r="G56" s="264"/>
+      <c r="H56" s="265"/>
+      <c r="I56" s="263">
+        <f>J53</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="264"/>
+      <c r="K56" s="265"/>
+      <c r="L56" s="263">
+        <f>M53</f>
+        <v>0</v>
+      </c>
+      <c r="M56" s="264"/>
+      <c r="N56" s="265"/>
+      <c r="O56" s="263">
+        <f>P53</f>
+        <v>0</v>
+      </c>
+      <c r="P56" s="264"/>
+      <c r="Q56" s="265"/>
+      <c r="R56" s="263">
+        <f>S53</f>
+        <v>0</v>
+      </c>
+      <c r="S56" s="264"/>
+      <c r="T56" s="265"/>
+      <c r="U56" s="263">
+        <f>V53</f>
+        <v>0</v>
+      </c>
+      <c r="V56" s="264"/>
+      <c r="W56" s="265"/>
+    </row>
+    <row r="57" spans="1:23" ht="50" customHeight="1" thickBot="1">
+      <c r="A57" s="262" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="262"/>
+      <c r="C57" s="266">
+        <f>C56*12</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="267"/>
+      <c r="E57" s="268"/>
+      <c r="F57" s="266">
+        <f t="shared" ref="F57" si="53">F56*12</f>
+        <v>0</v>
+      </c>
+      <c r="G57" s="267"/>
+      <c r="H57" s="268"/>
+      <c r="I57" s="266">
+        <f t="shared" ref="I57" si="54">I56*12</f>
+        <v>0</v>
+      </c>
+      <c r="J57" s="267"/>
+      <c r="K57" s="268"/>
+      <c r="L57" s="266">
+        <f t="shared" ref="L57" si="55">L56*12</f>
+        <v>0</v>
+      </c>
+      <c r="M57" s="267"/>
+      <c r="N57" s="268"/>
+      <c r="O57" s="266">
+        <f t="shared" ref="O57" si="56">O56*12</f>
+        <v>0</v>
+      </c>
+      <c r="P57" s="267"/>
+      <c r="Q57" s="268"/>
+      <c r="R57" s="266">
+        <f t="shared" ref="R57" si="57">R56*12</f>
+        <v>0</v>
+      </c>
+      <c r="S57" s="267"/>
+      <c r="T57" s="268"/>
+      <c r="U57" s="266">
+        <f t="shared" ref="U57" si="58">U56*12</f>
+        <v>0</v>
+      </c>
+      <c r="V57" s="267"/>
+      <c r="W57" s="268"/>
+    </row>
+    <row r="58" spans="1:23" ht="50" customHeight="1">
+      <c r="B58" s="234"/>
+      <c r="C58" s="234"/>
+      <c r="D58" s="234"/>
+      <c r="E58" s="234"/>
+      <c r="F58" s="234"/>
+      <c r="G58" s="234"/>
+      <c r="H58" s="234"/>
+      <c r="I58" s="234"/>
+      <c r="J58" s="234"/>
+      <c r="K58" s="234"/>
+      <c r="L58" s="234"/>
+      <c r="M58" s="234"/>
+      <c r="N58" s="234"/>
+      <c r="O58" s="234"/>
+      <c r="P58" s="234"/>
+      <c r="Q58" s="234"/>
+      <c r="R58" s="234"/>
+      <c r="S58" s="234"/>
+      <c r="T58" s="234"/>
+      <c r="U58" s="234"/>
+      <c r="V58" s="234"/>
+      <c r="W58" s="234"/>
+    </row>
+    <row r="59" spans="1:23" s="269" customFormat="1" ht="24" customHeight="1"/>
+    <row r="60" spans="1:23" ht="50" customHeight="1" thickBot="1"/>
+    <row r="61" spans="1:23" ht="50" customHeight="1" thickTop="1">
+      <c r="A61" s="270" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="271" t="s">
+        <v>64</v>
+      </c>
+      <c r="C61" s="272" t="str">
+        <f>IF(YEAR(C23)-C11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="D61" s="273"/>
+      <c r="E61" s="274"/>
+      <c r="F61" s="272" t="str">
+        <f t="shared" ref="F61" si="59">IF(YEAR(F23)-F11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="G61" s="273"/>
+      <c r="H61" s="274"/>
+      <c r="I61" s="272" t="str">
+        <f t="shared" ref="I61" si="60">IF(YEAR(I23)-I11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="J61" s="273"/>
+      <c r="K61" s="274"/>
+      <c r="L61" s="272" t="str">
+        <f t="shared" ref="L61" si="61">IF(YEAR(L23)-L11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="M61" s="273"/>
+      <c r="N61" s="274"/>
+      <c r="O61" s="272" t="str">
+        <f t="shared" ref="O61" si="62">IF(YEAR(O23)-O11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="P61" s="273"/>
+      <c r="Q61" s="274"/>
+      <c r="R61" s="272" t="str">
+        <f t="shared" ref="R61" si="63">IF(YEAR(R23)-R11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="S61" s="273"/>
+      <c r="T61" s="274"/>
+      <c r="U61" s="272" t="str">
+        <f t="shared" ref="U61" si="64">IF(YEAR(U23)-U11&lt;=1,"新築","中古")</f>
+        <v>中古</v>
+      </c>
+      <c r="V61" s="273"/>
+      <c r="W61" s="274"/>
+    </row>
+    <row r="62" spans="1:23" ht="50" customHeight="1">
+      <c r="A62" s="275"/>
+      <c r="B62" s="276" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="277" t="str">
+        <f>IF($B$7-YEAR(C23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="D62" s="278"/>
+      <c r="E62" s="279"/>
+      <c r="F62" s="277" t="str">
+        <f>IF($B$7-YEAR(F23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="G62" s="278"/>
+      <c r="H62" s="279"/>
+      <c r="I62" s="277" t="str">
+        <f>IF($B$7-YEAR(I23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="J62" s="278"/>
+      <c r="K62" s="279"/>
+      <c r="L62" s="277" t="str">
+        <f t="shared" ref="L62" si="65">IF($B$7-YEAR(L23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="M62" s="278"/>
+      <c r="N62" s="279"/>
+      <c r="O62" s="277" t="str">
+        <f>IF($B$7-YEAR(O23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="P62" s="278"/>
+      <c r="Q62" s="279"/>
+      <c r="R62" s="277" t="str">
+        <f>IF($B$7-YEAR(R23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="S62" s="278"/>
+      <c r="T62" s="279"/>
+      <c r="U62" s="277" t="str">
+        <f t="shared" ref="U62" si="66">IF($B$7-YEAR(U23)&gt;=6,"長期","短期")</f>
+        <v>長期</v>
+      </c>
+      <c r="V62" s="278"/>
+      <c r="W62" s="279"/>
+    </row>
+    <row r="63" spans="1:23" ht="50" customHeight="1">
+      <c r="A63" s="275"/>
+      <c r="B63" s="280" t="s">
+        <v>66</v>
+      </c>
+      <c r="C63" s="277">
+        <f>YEAR(C23)-C11</f>
+        <v>1900</v>
+      </c>
+      <c r="D63" s="278"/>
+      <c r="E63" s="279"/>
+      <c r="F63" s="277">
+        <f>YEAR(F23)-F11</f>
+        <v>1900</v>
+      </c>
+      <c r="G63" s="278"/>
+      <c r="H63" s="279"/>
+      <c r="I63" s="277">
+        <f t="shared" ref="I63" si="67">YEAR(I23)-I11</f>
+        <v>1900</v>
+      </c>
+      <c r="J63" s="278"/>
+      <c r="K63" s="279"/>
+      <c r="L63" s="277">
+        <f t="shared" ref="L63" si="68">YEAR(L23)-L11</f>
+        <v>1900</v>
+      </c>
+      <c r="M63" s="278"/>
+      <c r="N63" s="279"/>
+      <c r="O63" s="277">
+        <f t="shared" ref="O63" si="69">YEAR(O23)-O11</f>
+        <v>1900</v>
+      </c>
+      <c r="P63" s="278"/>
+      <c r="Q63" s="279"/>
+      <c r="R63" s="277">
+        <f t="shared" ref="R63" si="70">YEAR(R23)-R11</f>
+        <v>1900</v>
+      </c>
+      <c r="S63" s="278"/>
+      <c r="T63" s="279"/>
+      <c r="U63" s="277">
+        <f t="shared" ref="U63" si="71">YEAR(U23)-U11</f>
+        <v>1900</v>
+      </c>
+      <c r="V63" s="278"/>
+      <c r="W63" s="279"/>
+    </row>
+    <row r="64" spans="1:23" ht="50" customHeight="1" thickBot="1">
+      <c r="A64" s="281"/>
+      <c r="B64" s="282" t="s">
+        <v>67</v>
+      </c>
+      <c r="C64" s="283" t="str">
+        <f>[1]空室・完済売却!C71</f>
         <v/>
       </c>
-      <c r="D26" s="36"/>
-      <c r="E26" s="24" t="str">
-        <f>IFERROR(C26/12,"")</f>
+      <c r="D64" s="284"/>
+      <c r="E64" s="285"/>
+      <c r="F64" s="283" t="str">
+        <f>[1]空室・完済売却!F71</f>
         <v/>
       </c>
-      <c r="F26" s="35" t="str">
-        <f>IF(F1="","",59000)</f>
+      <c r="G64" s="284"/>
+      <c r="H64" s="285"/>
+      <c r="I64" s="283" t="str">
+        <f>[1]空室・完済売却!I71</f>
         <v/>
       </c>
-      <c r="G26" s="36"/>
-      <c r="H26" s="24" t="str">
-        <f>IFERROR(F26/12,"")</f>
+      <c r="J64" s="284"/>
+      <c r="K64" s="285"/>
+      <c r="L64" s="283" t="str">
+        <f>[1]空室・完済売却!L71</f>
         <v/>
       </c>
-      <c r="I26" s="35" t="str">
-        <f>IF(I1="","",59000)</f>
-        <v/>
-      </c>
-      <c r="J26" s="36"/>
-      <c r="K26" s="24" t="str">
-        <f>IFERROR(I26/12,"")</f>
-        <v/>
-      </c>
-      <c r="L26" s="35" t="str">
-        <f>IF(L1="","",59000)</f>
-        <v/>
-      </c>
-      <c r="M26" s="36"/>
-      <c r="N26" s="24" t="str">
-        <f>IFERROR(L26/12,"")</f>
-        <v/>
-      </c>
+      <c r="M64" s="284"/>
+      <c r="N64" s="285"/>
+      <c r="O64" s="283">
+        <f>[1]空室・完済売却!O71</f>
+        <v>0</v>
+      </c>
+      <c r="P64" s="284"/>
+      <c r="Q64" s="285"/>
+      <c r="R64" s="283">
+        <f>[1]空室・完済売却!R71</f>
+        <v>0</v>
+      </c>
+      <c r="S64" s="284"/>
+      <c r="T64" s="285"/>
+      <c r="U64" s="283">
+        <f>[1]空室・完済売却!R71</f>
+        <v>0</v>
+      </c>
+      <c r="V64" s="284"/>
+      <c r="W64" s="285"/>
     </row>
-    <row r="27" spans="1:14" ht="32" thickTop="1">
-      <c r="A27" s="101" t="s">
-        <v>22</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="37" t="str">
-        <f>IFERROR(IF(D18-SUM(C19:C25)-E26=0,"",D18-SUM(C19:C25)-E26),"")</f>
-        <v/>
-      </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="37" t="str">
-        <f>IFERROR(IF(G18-SUM(F19:F25)-H26=0,"",G18-SUM(F19:F25)-H26),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="38"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="37" t="str">
-        <f>IFERROR(IF(J18-SUM(I19:I25)-K26=0,"",J18-SUM(I19:I25)-K26),"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="38"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="37" t="str">
-        <f>IFERROR(IF(M18-SUM(L19:L25)-N26=0,"",M18-SUM(L19:L25)-N26),"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="38"/>
-      <c r="N27" s="39"/>
-    </row>
-    <row r="28" spans="1:14" ht="31">
-      <c r="A28" s="102"/>
-      <c r="B28" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="40" t="str">
-        <f>IF(C27="","",C27*12)</f>
-        <v/>
-      </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="40" t="str">
-        <f>IF(F27="","",F27*12)</f>
-        <v/>
-      </c>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="40" t="str">
-        <f>IF(I27="","",I27*12)</f>
-        <v/>
-      </c>
-      <c r="J28" s="41"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="40" t="str">
-        <f>IF(L27="","",L27*12)</f>
-        <v/>
-      </c>
-      <c r="M28" s="41"/>
-      <c r="N28" s="42"/>
-    </row>
-    <row r="29" spans="1:14" ht="47" thickBot="1">
-      <c r="A29" s="103"/>
-      <c r="B29" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C29" s="29" t="str">
-        <f ca="1">IF(OR(C27="",E15=""),"",C27*E15)</f>
-        <v/>
-      </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="29" t="str">
-        <f ca="1">IF(OR(F27="",H15=""),"",F27*H15)</f>
-        <v/>
-      </c>
-      <c r="G29" s="30"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="29" t="str">
-        <f ca="1">IF(OR(I27="",K15=""),"",I27*K15)</f>
-        <v/>
-      </c>
-      <c r="J29" s="30"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="29" t="str">
-        <f ca="1">IF(OR(L27="",N15=""),"",L27*N15)</f>
-        <v/>
-      </c>
-      <c r="M29" s="30"/>
-      <c r="N29" s="31"/>
-    </row>
-    <row r="30" spans="1:14" ht="21" thickTop="1"/>
+    <row r="65" ht="15" thickTop="1"/>
   </sheetData>
-  <mergeCells count="112">
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:E21"/>
-    <mergeCell ref="A22:A26"/>
+  <mergeCells count="406">
+    <mergeCell ref="U12:W12"/>
+    <mergeCell ref="AW12:AX12"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:Q12"/>
+    <mergeCell ref="R12:T12"/>
+    <mergeCell ref="O63:Q63"/>
+    <mergeCell ref="R63:T63"/>
+    <mergeCell ref="U63:W63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:H64"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="L64:N64"/>
+    <mergeCell ref="O64:Q64"/>
+    <mergeCell ref="R64:T64"/>
+    <mergeCell ref="U64:W64"/>
+    <mergeCell ref="R61:T61"/>
+    <mergeCell ref="U61:W61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:H62"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="L62:N62"/>
+    <mergeCell ref="O62:Q62"/>
+    <mergeCell ref="R62:T62"/>
+    <mergeCell ref="U62:W62"/>
+    <mergeCell ref="A61:A64"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:H61"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="L61:N61"/>
+    <mergeCell ref="O61:Q61"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="F63:H63"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="L63:N63"/>
+    <mergeCell ref="R56:T56"/>
+    <mergeCell ref="U56:W56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="L57:N57"/>
+    <mergeCell ref="O57:Q57"/>
+    <mergeCell ref="R57:T57"/>
+    <mergeCell ref="U57:W57"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="L56:N56"/>
+    <mergeCell ref="O56:Q56"/>
+    <mergeCell ref="V53:W53"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="I55:J55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="R55:S55"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="S53:T53"/>
+    <mergeCell ref="S51:T51"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="G52:H52"/>
+    <mergeCell ref="J52:K52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="S52:T52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="R44:S44"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="S48:T48"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="O37:Q37"/>
+    <mergeCell ref="R37:T37"/>
+    <mergeCell ref="U37:W37"/>
+    <mergeCell ref="X37:Z37"/>
+    <mergeCell ref="R35:T35"/>
+    <mergeCell ref="U35:W35"/>
+    <mergeCell ref="X35:Z35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="X33:Z34"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="R34:S34"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="R32:T32"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="R33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="X30:Z31"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="U31:W31"/>
+    <mergeCell ref="A30:A34"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="V26:W26"/>
+    <mergeCell ref="X26:Z26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="C27:E29"/>
+    <mergeCell ref="F27:H29"/>
+    <mergeCell ref="I27:K29"/>
+    <mergeCell ref="L27:N29"/>
+    <mergeCell ref="O27:Q29"/>
+    <mergeCell ref="R27:T29"/>
+    <mergeCell ref="U27:W29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="AW24:AX35"/>
+    <mergeCell ref="AY24:AZ35"/>
+    <mergeCell ref="BA24:BB35"/>
+    <mergeCell ref="BC24:BD35"/>
+    <mergeCell ref="BE24:BF35"/>
+    <mergeCell ref="BG24:BH35"/>
+    <mergeCell ref="W23:W24"/>
+    <mergeCell ref="X23:Z25"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="R24:S24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="N23:N24"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:Q24"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="T23:T24"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="U22:W22"/>
+    <mergeCell ref="AW22:AX22"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="K23:K24"/>
+    <mergeCell ref="L23:M23"/>
     <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="A8:A17"/>
-    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="R22:T22"/>
+    <mergeCell ref="AW20:AX20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="R21:T21"/>
+    <mergeCell ref="U21:W21"/>
+    <mergeCell ref="AW21:AX21"/>
+    <mergeCell ref="R19:T19"/>
+    <mergeCell ref="U19:W19"/>
+    <mergeCell ref="X19:Z19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="R20:T20"/>
+    <mergeCell ref="U20:W20"/>
+    <mergeCell ref="CR18:CR19"/>
+    <mergeCell ref="CS18:CS19"/>
+    <mergeCell ref="CT18:CT19"/>
+    <mergeCell ref="CU18:CU19"/>
+    <mergeCell ref="CV18:CV19"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="CL18:CL19"/>
+    <mergeCell ref="CM18:CM19"/>
+    <mergeCell ref="CN18:CN19"/>
+    <mergeCell ref="CO18:CO19"/>
+    <mergeCell ref="CP18:CP19"/>
+    <mergeCell ref="CQ18:CQ19"/>
+    <mergeCell ref="CF18:CF19"/>
+    <mergeCell ref="CG18:CG19"/>
+    <mergeCell ref="CH18:CH19"/>
+    <mergeCell ref="CI18:CI19"/>
+    <mergeCell ref="CJ18:CJ19"/>
+    <mergeCell ref="CK18:CK19"/>
+    <mergeCell ref="BZ18:BZ19"/>
+    <mergeCell ref="CA18:CA19"/>
+    <mergeCell ref="CB18:CB19"/>
+    <mergeCell ref="CC18:CC19"/>
+    <mergeCell ref="CD18:CD19"/>
+    <mergeCell ref="CE18:CE19"/>
+    <mergeCell ref="BT18:BT19"/>
+    <mergeCell ref="BU18:BU19"/>
+    <mergeCell ref="BV18:BV19"/>
+    <mergeCell ref="BW18:BW19"/>
+    <mergeCell ref="BX18:BX19"/>
+    <mergeCell ref="BY18:BY19"/>
+    <mergeCell ref="BN18:BN19"/>
+    <mergeCell ref="BO18:BO19"/>
+    <mergeCell ref="BP18:BP19"/>
+    <mergeCell ref="BQ18:BQ19"/>
+    <mergeCell ref="BR18:BR19"/>
+    <mergeCell ref="BS18:BS19"/>
+    <mergeCell ref="BH18:BH19"/>
+    <mergeCell ref="BI18:BI19"/>
+    <mergeCell ref="BJ18:BJ19"/>
+    <mergeCell ref="BK18:BK19"/>
+    <mergeCell ref="BL18:BL19"/>
+    <mergeCell ref="BM18:BM19"/>
+    <mergeCell ref="BB18:BB19"/>
+    <mergeCell ref="BC18:BC19"/>
+    <mergeCell ref="BD18:BD19"/>
+    <mergeCell ref="BE18:BE19"/>
+    <mergeCell ref="BF18:BF19"/>
+    <mergeCell ref="BG18:BG19"/>
+    <mergeCell ref="U18:W18"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="AW18:AX19"/>
+    <mergeCell ref="AY18:AY19"/>
+    <mergeCell ref="AZ18:AZ19"/>
+    <mergeCell ref="BA18:BA19"/>
+    <mergeCell ref="AH17:AI17"/>
+    <mergeCell ref="AK17:AL17"/>
+    <mergeCell ref="AW17:AX17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="R18:T18"/>
+    <mergeCell ref="AH16:AI16"/>
+    <mergeCell ref="AJ16:AJ17"/>
+    <mergeCell ref="AK16:AL16"/>
+    <mergeCell ref="AW16:AX16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:T17"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="U16:W16"/>
+    <mergeCell ref="AB16:AC16"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="U17:W17"/>
+    <mergeCell ref="X17:Z17"/>
+    <mergeCell ref="AB17:AC17"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="AE15:AF15"/>
+    <mergeCell ref="AH15:AI15"/>
+    <mergeCell ref="AK15:AL15"/>
+    <mergeCell ref="AW15:AX15"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="AB14:AL14"/>
+    <mergeCell ref="AW14:AX14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="R15:T15"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="AB15:AC15"/>
+    <mergeCell ref="U13:W13"/>
+    <mergeCell ref="AW13:AX13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="R14:T14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="R13:T13"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AI9:AJ9"/>
+    <mergeCell ref="AI10:AJ11"/>
+    <mergeCell ref="AK10:AK11"/>
+    <mergeCell ref="AB11:AC11"/>
+    <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="AK8:AK9"/>
+    <mergeCell ref="AL8:AL9"/>
+    <mergeCell ref="AM8:AM9"/>
+    <mergeCell ref="AN8:AN9"/>
     <mergeCell ref="C9:E9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F8:H8"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="F19:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I1:K1"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
     <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="L8:N8"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="I19:K21"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="L19:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="AW6:AY11"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="V8:W8"/>
+    <mergeCell ref="S2:T3"/>
+    <mergeCell ref="U2:W3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="Q4:W4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="Q5:W5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="Q6:W6"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C3"/>
+    <mergeCell ref="D2:E3"/>
+    <mergeCell ref="J2:K3"/>
+    <mergeCell ref="L2:N3"/>
+    <mergeCell ref="P2:Q3"/>
   </mergeCells>
-  <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="C1:N2 C3 E3:F3 H3:I3 K3:L3 N3 C4:N5 C7:N9 C12:N12 C14:N14 C15:D15 F15:G15 I15:J15 L15:M15 D18:E18 G18:H18 J18:K18 M18:N18 C22:N25">
-    <cfRule type="containsBlanks" dxfId="14" priority="21">
-      <formula>LEN(TRIM(C1))=0</formula>
+  <phoneticPr fontId="2"/>
+  <conditionalFormatting sqref="C51">
+    <cfRule type="cellIs" dxfId="32" priority="20" operator="equal">
+      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:N29">
-    <cfRule type="cellIs" dxfId="13" priority="3" operator="greaterThan">
+  <conditionalFormatting sqref="C35:W37">
+    <cfRule type="cellIs" dxfId="30" priority="30" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="cellIs" dxfId="11" priority="22" operator="between">
-      <formula>30</formula>
-      <formula>70</formula>
+  <conditionalFormatting sqref="C62:W64">
+    <cfRule type="cellIs" dxfId="28" priority="13" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="23" operator="between">
-      <formula>20</formula>
-      <formula>29</formula>
+    <cfRule type="cellIs" dxfId="27" priority="14" operator="lessThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17">
-    <cfRule type="cellIs" dxfId="9" priority="26" operator="lessThan">
-      <formula>10</formula>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="containsText" dxfId="26" priority="24" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",D8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="between">
-      <formula>30</formula>
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="12" operator="between">
-      <formula>20</formula>
-      <formula>29</formula>
+  <conditionalFormatting sqref="F51">
+    <cfRule type="cellIs" dxfId="22" priority="19" operator="equal">
+      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H17">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="lessThan">
-      <formula>10</formula>
+  <conditionalFormatting sqref="G8">
+    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",G8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
-      <formula>30</formula>
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="between">
-      <formula>20</formula>
-      <formula>29</formula>
+  <conditionalFormatting sqref="I51">
+    <cfRule type="cellIs" dxfId="19" priority="18" operator="equal">
+      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K17">
-    <cfRule type="cellIs" dxfId="3" priority="10" operator="lessThan">
-      <formula>10</formula>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="containsText" dxfId="18" priority="22" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",J8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="between">
-      <formula>30</formula>
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>20</formula>
-      <formula>29</formula>
+  <conditionalFormatting sqref="L51">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
+      <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N17">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="lessThan">
-      <formula>10</formula>
+  <conditionalFormatting sqref="M8">
+    <cfRule type="containsText" dxfId="15" priority="21" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",M8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18 F18 I18 L18" xr:uid="{779087AD-0721-4B4B-B9B1-B4AF7A8C847E}">
+  <conditionalFormatting sqref="O51">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P8">
+    <cfRule type="containsText" dxfId="12" priority="10" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",P8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R51">
+    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S8">
+    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",S8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U51">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V8">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="1900">
+      <formula>NOT(ISERROR(SEARCH("1900",V8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE16:AF16">
+    <cfRule type="cellIs" dxfId="2" priority="26" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH16:AI16">
+    <cfRule type="cellIs" dxfId="1" priority="25" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AW21:CV22 AW24 AY24 BA24 BC24 BE24 BG24">
+    <cfRule type="cellIs" dxfId="0" priority="27" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C26 F26 O26 I26 L26 R26 U26" xr:uid="{7503DA9E-4D7E-4E47-8E99-1649A2C39F5D}">
       <formula1>"自主管理,集金代行,空室,通帳入金,サブリース,マスターリース,募集賃料,先賃,エステム特殊契約"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:N4 Q4 T4:W4" xr:uid="{72F1CFB4-39E3-DF49-A09D-F24D4E4EA46F}">
+      <formula1>"〒153-0043　東京都目黒区東山1-4-4,〒154-0001　東京都世田谷区池尻2-37-12"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2 U2" xr:uid="{204089A0-A3B6-4D41-B03E-6419469895C3}">
+      <formula1>"株式会社エルズホーム,スマイルエージェント株式会社"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5 Q5 T5" xr:uid="{1DAA391D-7B84-FB43-A6C3-64E457E404A5}">
+      <formula1>"TEL：03-5794-5151　FAX：03-5794-5161,TEL：03-5433-1521　FAX：03-5433-1522"</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="1.2204724409448819" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="38" orientation="landscape" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>